--- a/Link block explorer for major networks.xlsx
+++ b/Link block explorer for major networks.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Explorers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Networks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Explorers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Networks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14,7 +14,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -42,21 +42,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <color theme="1"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <color rgb="FF000000"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="FF0000FF"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF0000FF"/>
+      <u val="single"/>
+    </font>
+    <font>
       <name val="Calibri"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="12"/>
     </font>
@@ -66,20 +68,13 @@
       <u val="single"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
+      <name val="Arial"/>
+      <color rgb="FF0000FF"/>
       <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color theme="1"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -98,18 +93,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBDFC2"/>
-        <bgColor rgb="FFFBDFC2"/>
+        <fgColor rgb="FFF9D8B5"/>
+        <bgColor rgb="FFF9D8B5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1E6C9"/>
-        <bgColor rgb="FFD1E6C9"/>
+        <fgColor rgb="FFC7E1BD"/>
+        <bgColor rgb="FFC7E1BD"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="26">
     <border/>
     <border>
       <left style="thin">
@@ -141,7 +136,77 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF888888"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF888888"/>
+      </top>
+      <bottom style="thin">
         <color rgb="FFB4B4B4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF888888"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9A9A9A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4B4B4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA5A5A5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4B4B4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA5A5A5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF888888"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF888888"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF888888"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF888888"/>
       </left>
       <right style="thin">
         <color rgb="FF9A9A9A"/>
@@ -155,13 +220,97 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4B4B4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA5A5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA5A5A5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA5A5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF9A9A9A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4B4B4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF888888"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA5A5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA5A5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF888888"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA5A5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF888888"/>
       </left>
       <right style="thin">
         <color rgb="FF9A9A9A"/>
       </right>
       <top style="thin">
-        <color rgb="FFB4B4B4"/>
+        <color rgb="FF9A9A9A"/>
       </top>
       <bottom style="thin">
         <color rgb="FFB4B4B4"/>
@@ -186,6 +335,48 @@
         <color rgb="FFB4B4B4"/>
       </left>
       <right style="thin">
+        <color rgb="FFA5A5A5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF888888"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA5A5A5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA5A5A5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA5A5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF757575"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA5A5A5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA5A5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF757575"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right style="thin">
         <color rgb="FFB4B4B4"/>
       </right>
       <top style="thin">
@@ -197,10 +388,66 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9A9A9A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9A9A9A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9A9A9A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF888888"/>
       </left>
       <right style="thin">
+        <color rgb="FF757575"/>
+      </right>
+      <top style="thin">
         <color rgb="FF888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF888888"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF757575"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF757575"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF757575"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF757575"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF757575"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF757575"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF757575"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9A9A9A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF757575"/>
       </right>
       <top style="thin">
         <color rgb="FF888888"/>
@@ -213,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -242,58 +489,100 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -575,19 +864,19 @@
   <dimension ref="A1:J1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="20.88" customWidth="1" style="30" min="1" max="1"/>
-    <col width="47.63" customWidth="1" style="30" min="2" max="2"/>
-    <col width="20" customWidth="1" style="30" min="3" max="3"/>
-    <col width="29.13" customWidth="1" style="30" min="4" max="4"/>
-    <col width="44.88" customWidth="1" style="30" min="5" max="5"/>
-    <col width="39.75" customWidth="1" style="30" min="6" max="6"/>
-    <col width="26.13" customWidth="1" style="30" min="7" max="7"/>
-    <col width="15.13" customWidth="1" style="30" min="8" max="8"/>
-    <col width="37.63" customWidth="1" style="30" min="9" max="9"/>
-    <col width="39.5" customWidth="1" style="30" min="10" max="10"/>
+    <col width="20.88" customWidth="1" style="42" min="1" max="1"/>
+    <col width="47.63" customWidth="1" style="42" min="2" max="2"/>
+    <col width="20" customWidth="1" style="42" min="3" max="3"/>
+    <col width="29.13" customWidth="1" style="42" min="4" max="4"/>
+    <col width="44.88" customWidth="1" style="42" min="5" max="5"/>
+    <col width="39.75" customWidth="1" style="42" min="6" max="6"/>
+    <col width="26.13" customWidth="1" style="42" min="7" max="7"/>
+    <col width="15.13" customWidth="1" style="42" min="8" max="8"/>
+    <col width="37.63" customWidth="1" style="42" min="9" max="9"/>
+    <col width="39.5" customWidth="1" style="42" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1" s="30">
+    <row r="1" ht="20.25" customHeight="1" s="42">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
@@ -698,7 +987,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Ethereum, Gnosis Chain, Ethereum Classic, Base, Optimism, Arbitrum One, Polygon, zkSync Era, Scroll, Linea</t>
+          <t>Ethereum, Gnosis Chain, Ethereum Classic, Base, Optimism, Arbitrum One, Polygon, zkSync Era, Scroll, Linea, and more</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -2630,11 +2919,64 @@
       <c r="J48" s="6" t="n"/>
     </row>
     <row r="49">
-      <c r="C49" s="7" t="n"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Gnosis Beacon Chain Explorer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Gnosis Beacon Chain Explorer is the official validator and staking explorer for the Gnosis Beacon Chain, built by Bitfly. It provides detailed data on validators, epochs, slots, and staking rewards on the Gnosis network.</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Gnosis Chain</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://beaconchain.gnosischain.com</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://github.com/gobitfly/eth2-beaconchain-explorer</t>
+        </is>
+      </c>
       <c r="H49" s="8" t="n"/>
     </row>
     <row r="50">
-      <c r="C50" s="7" t="n"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3xpl</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3xpl is a universal blockchain explorer supporting 48+ blockchains including Gnosis Chain, offering lightning-fast block and transaction lookup with no ads and maximum privacy.</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Gnosis Chain</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://3xpl.com</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://x.com/3xplcom</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://github.com/3xplcom</t>
+        </is>
+      </c>
       <c r="H50" s="8" t="n"/>
     </row>
     <row r="51">
@@ -6643,15 +6985,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W57"/>
+  <dimension ref="A1:W46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="17.25" customWidth="1" style="30" min="1" max="1"/>
-    <col width="17.63" customWidth="1" style="30" min="2" max="2"/>
-    <col width="20.88" customWidth="1" style="30" min="3" max="3"/>
-    <col width="46.13" customWidth="1" style="30" min="4" max="4"/>
-    <col width="26.63" customWidth="1" style="30" min="5" max="5"/>
-    <col width="24.38" customWidth="1" style="30" min="6" max="6"/>
+    <col width="17.25" customWidth="1" style="42" min="1" max="1"/>
+    <col width="17.63" customWidth="1" style="42" min="2" max="2"/>
+    <col width="20.88" customWidth="1" style="42" min="3" max="3"/>
+    <col width="46.13" customWidth="1" style="42" min="4" max="4"/>
+    <col width="26.63" customWidth="1" style="42" min="5" max="5"/>
+    <col width="24.38" customWidth="1" style="42" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6692,7 +7034,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Ethereum</t>
         </is>
@@ -6712,29 +7054,45 @@
           <t>Ethereum is the leading decentralized smart contract platform enabling DeFi, NFTs, and dApps through its EVM. It transitioned to proof-of-stake via The Merge in 2022.</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>https://x.com/ethereum</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>https://ethereum.org</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
+      <c r="H2" s="16" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="6" t="n"/>
+      <c r="N2" s="6" t="n"/>
+      <c r="O2" s="6" t="n"/>
+      <c r="P2" s="6" t="n"/>
+      <c r="Q2" s="6" t="n"/>
+      <c r="R2" s="6" t="n"/>
+      <c r="S2" s="6" t="n"/>
+      <c r="T2" s="6" t="n"/>
+      <c r="U2" s="6" t="n"/>
+      <c r="V2" s="6" t="n"/>
+      <c r="W2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Mempool.space</t>
         </is>
@@ -6749,34 +7107,50 @@
           <t>Bitcoin is the world's first decentralized peer-to-peer digital currency, created by Satoshi Nakamoto in 2009 and secured by proof-of-work mining.</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>https://x.com/bitcoin</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>https://bitcoin.org</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
+      <c r="H3" s="16" t="n"/>
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="6" t="n"/>
+      <c r="N3" s="6" t="n"/>
+      <c r="O3" s="6" t="n"/>
+      <c r="P3" s="6" t="n"/>
+      <c r="Q3" s="6" t="n"/>
+      <c r="R3" s="6" t="n"/>
+      <c r="S3" s="6" t="n"/>
+      <c r="T3" s="6" t="n"/>
+      <c r="U3" s="6" t="n"/>
+      <c r="V3" s="6" t="n"/>
+      <c r="W3" s="6" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Solana</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Solscan</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Solana Explorer</t>
         </is>
@@ -6786,34 +7160,50 @@
           <t>Solana is a high-performance Layer-1 blockchain using Proof of History and Proof of Stake, capable of processing thousands of transactions per second with low fees.</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>https://x.com/solana</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>https://solana.com</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>Solana</t>
         </is>
       </c>
+      <c r="H4" s="16" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="6" t="n"/>
+      <c r="P4" s="6" t="n"/>
+      <c r="Q4" s="6" t="n"/>
+      <c r="R4" s="6" t="n"/>
+      <c r="S4" s="6" t="n"/>
+      <c r="T4" s="6" t="n"/>
+      <c r="U4" s="6" t="n"/>
+      <c r="V4" s="6" t="n"/>
+      <c r="W4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Avalanche</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Avascan</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>SnowScan</t>
         </is>
@@ -6823,34 +7213,50 @@
           <t>Avalanche is a Layer-1 blockchain with a multi-chain architecture (C-Chain, X-Chain, P-Chain) offering high throughput and sub-second finality via the Avalanche consensus protocol.</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>https://x.com/avax</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>https://avax.network</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>Avalanche</t>
         </is>
       </c>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="6" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="6" t="n"/>
+      <c r="Q5" s="6" t="n"/>
+      <c r="R5" s="6" t="n"/>
+      <c r="S5" s="6" t="n"/>
+      <c r="T5" s="6" t="n"/>
+      <c r="U5" s="6" t="n"/>
+      <c r="V5" s="6" t="n"/>
+      <c r="W5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Cardano</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>CardanoScan</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Adastat</t>
         </is>
@@ -6860,34 +7266,50 @@
           <t>Cardano is a peer-reviewed proof-of-stake blockchain developed by IOHK, featuring the Ouroboros consensus protocol and native multi-asset and NFT support.</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>https://x.com/cardano</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>https://cardano.org</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>Cardano</t>
         </is>
       </c>
+      <c r="H6" s="16" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="n"/>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="6" t="n"/>
+      <c r="T6" s="6" t="n"/>
+      <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
+      <c r="W6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>XRP Ledger</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>XRPScan</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Bithomp</t>
         </is>
@@ -6897,34 +7319,50 @@
           <t>The XRP Ledger is a fast, energy-efficient public blockchain built for global payments, featuring a built-in DEX, NFT support, and the XRP Consensus Protocol.</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>https://x.com/XRPLedger</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>https://xrpl.org</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>XRP</t>
         </is>
       </c>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Starknet</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Starkscan</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>Voyager</t>
         </is>
@@ -6934,2315 +7372,2043 @@
           <t>Starknet is a permissionless ZK rollup on Ethereum developed by StarkWare, using STARK cryptographic proofs for scalable computation with native account abstraction.</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>https://x.com/Starknet</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>https://starknet.io</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>Starknet</t>
         </is>
       </c>
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="6" t="n"/>
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="6" t="n"/>
+      <c r="T8" s="6" t="n"/>
+      <c r="U8" s="6" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Ethereum Classic</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Blockscout (ETC)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>OKLink</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Ethereum Classic is the original Ethereum blockchain that preserved immutability after the 2016 DAO hack, supporting smart contracts and secured by proof-of-work.</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>https://x.com/eth_classic</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>https://ethereumclassic.org</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>Ethereum Classic</t>
         </is>
       </c>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="26" t="n"/>
+      <c r="J9" s="26" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="6" t="n"/>
+      <c r="R9" s="6" t="n"/>
+      <c r="S9" s="6" t="n"/>
+      <c r="T9" s="6" t="n"/>
+      <c r="U9" s="6" t="n"/>
+      <c r="V9" s="6" t="n"/>
+      <c r="W9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Gnosis</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Gnosisscan</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>Gnosis Chain (formerly xDai Chain) is a stable, EVM-compatible Layer-1 blockchain using xDAI as its gas token, secured by a permissionless set of validators.</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>https://x.com/gnosischain</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>https://www.gnosischain.com</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="E10" s="30" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="31" t="inlineStr">
         <is>
           <t>xDai</t>
         </is>
       </c>
-      <c r="H10" s="23" t="n"/>
-      <c r="I10" s="23" t="n"/>
-      <c r="J10" s="23" t="n"/>
-      <c r="K10" s="24" t="n"/>
-      <c r="L10" s="24" t="n"/>
-      <c r="M10" s="24" t="n"/>
-      <c r="N10" s="24" t="n"/>
-      <c r="O10" s="24" t="n"/>
-      <c r="P10" s="24" t="n"/>
-      <c r="Q10" s="24" t="n"/>
-      <c r="R10" s="24" t="n"/>
-      <c r="S10" s="24" t="n"/>
-      <c r="T10" s="24" t="n"/>
-      <c r="U10" s="24" t="n"/>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="24" t="n"/>
+      <c r="H10" s="32" t="n"/>
+      <c r="I10" s="32" t="n"/>
+      <c r="J10" s="32" t="n"/>
+      <c r="K10" s="33" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="6" t="n"/>
+      <c r="Q10" s="6" t="n"/>
+      <c r="R10" s="6" t="n"/>
+      <c r="S10" s="6" t="n"/>
+      <c r="T10" s="6" t="n"/>
+      <c r="U10" s="6" t="n"/>
+      <c r="V10" s="6" t="n"/>
+      <c r="W10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>BaseScan</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>Base is an Ethereum Layer-2 network built by Coinbase using the OP Stack, offering low-cost EVM-compatible transactions with seamless access to Coinbase's ecosystem.</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>https://x.com/base</t>
         </is>
       </c>
-      <c r="F11" s="27" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>https://base.org</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="38" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H11" s="28" t="n"/>
-      <c r="I11" s="29" t="n"/>
-      <c r="J11" s="29" t="n"/>
-      <c r="K11" s="24" t="n"/>
-      <c r="L11" s="24" t="n"/>
-      <c r="M11" s="24" t="n"/>
-      <c r="N11" s="24" t="n"/>
-      <c r="O11" s="24" t="n"/>
-      <c r="P11" s="24" t="n"/>
-      <c r="Q11" s="24" t="n"/>
-      <c r="R11" s="24" t="n"/>
-      <c r="S11" s="24" t="n"/>
-      <c r="T11" s="24" t="n"/>
-      <c r="U11" s="24" t="n"/>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="24" t="n"/>
+      <c r="H11" s="39" t="n"/>
+      <c r="I11" s="39" t="n"/>
+      <c r="J11" s="39" t="n"/>
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="n"/>
+      <c r="R11" s="6" t="n"/>
+      <c r="S11" s="6" t="n"/>
+      <c r="T11" s="6" t="n"/>
+      <c r="U11" s="6" t="n"/>
+      <c r="V11" s="6" t="n"/>
+      <c r="W11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Optimism</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>Optimistic Etherscan</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>Optimism is an Ethereum Layer-2 optimistic rollup providing EVM-equivalent scalability with a fraud-proof security model, governed by the Optimism Collective.</t>
         </is>
       </c>
-      <c r="E12" s="27" t="inlineStr">
+      <c r="E12" s="37" t="inlineStr">
         <is>
           <t>https://x.com/optimismFND</t>
         </is>
       </c>
-      <c r="F12" s="27" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>https://optimism.io</t>
         </is>
       </c>
-      <c r="G12" s="27" t="inlineStr">
+      <c r="G12" s="40" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H12" s="28" t="n"/>
-      <c r="I12" s="29" t="n"/>
-      <c r="J12" s="29" t="n"/>
-      <c r="K12" s="24" t="n"/>
-      <c r="L12" s="24" t="n"/>
-      <c r="M12" s="24" t="n"/>
-      <c r="N12" s="24" t="n"/>
-      <c r="O12" s="24" t="n"/>
-      <c r="P12" s="24" t="n"/>
-      <c r="Q12" s="24" t="n"/>
-      <c r="R12" s="24" t="n"/>
-      <c r="S12" s="24" t="n"/>
-      <c r="T12" s="24" t="n"/>
-      <c r="U12" s="24" t="n"/>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="24" t="n"/>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="39" t="n"/>
+      <c r="J12" s="39" t="n"/>
+      <c r="K12" s="16" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="n"/>
+      <c r="R12" s="6" t="n"/>
+      <c r="S12" s="6" t="n"/>
+      <c r="T12" s="6" t="n"/>
+      <c r="U12" s="6" t="n"/>
+      <c r="V12" s="6" t="n"/>
+      <c r="W12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Arbitrum One</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Arbiscan</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>Arbitrum One is an Ethereum Layer-2 optimistic rollup developed by Offchain Labs, delivering high throughput and low fees with full EVM compatibility.</t>
         </is>
       </c>
-      <c r="E13" s="27" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>https://x.com/arbitrum</t>
         </is>
       </c>
-      <c r="F13" s="27" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>https://arbitrum.io</t>
         </is>
       </c>
-      <c r="G13" s="27" t="inlineStr">
+      <c r="G13" s="40" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H13" s="28" t="n"/>
-      <c r="I13" s="29" t="n"/>
-      <c r="J13" s="29" t="n"/>
-      <c r="K13" s="24" t="n"/>
-      <c r="L13" s="24" t="n"/>
-      <c r="M13" s="24" t="n"/>
-      <c r="N13" s="24" t="n"/>
-      <c r="O13" s="24" t="n"/>
-      <c r="P13" s="24" t="n"/>
-      <c r="Q13" s="24" t="n"/>
-      <c r="R13" s="24" t="n"/>
-      <c r="S13" s="24" t="n"/>
-      <c r="T13" s="24" t="n"/>
-      <c r="U13" s="24" t="n"/>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="24" t="n"/>
+      <c r="H13" s="39" t="n"/>
+      <c r="I13" s="39" t="n"/>
+      <c r="J13" s="39" t="n"/>
+      <c r="K13" s="16" t="n"/>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="6" t="n"/>
+      <c r="R13" s="6" t="n"/>
+      <c r="S13" s="6" t="n"/>
+      <c r="T13" s="6" t="n"/>
+      <c r="U13" s="6" t="n"/>
+      <c r="V13" s="6" t="n"/>
+      <c r="W13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>Polygon</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Polygonscan</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>Polygon PoS is an EVM-compatible proof-of-stake commit chain anchored to Ethereum, providing fast and affordable transactions for DeFi and dApp protocols.</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>https://x.com/0xpolygon</t>
         </is>
       </c>
-      <c r="F14" s="27" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>https://polygon.technology</t>
         </is>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="38" t="inlineStr">
         <is>
           <t>Polygon Ecosystem Token</t>
         </is>
       </c>
-      <c r="H14" s="28" t="n"/>
-      <c r="I14" s="29" t="n"/>
-      <c r="J14" s="29" t="n"/>
-      <c r="K14" s="24" t="n"/>
-      <c r="L14" s="24" t="n"/>
-      <c r="M14" s="24" t="n"/>
-      <c r="N14" s="24" t="n"/>
-      <c r="O14" s="24" t="n"/>
-      <c r="P14" s="24" t="n"/>
-      <c r="Q14" s="24" t="n"/>
-      <c r="R14" s="24" t="n"/>
-      <c r="S14" s="24" t="n"/>
-      <c r="T14" s="24" t="n"/>
-      <c r="U14" s="24" t="n"/>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="24" t="n"/>
+      <c r="H14" s="39" t="n"/>
+      <c r="I14" s="39" t="n"/>
+      <c r="J14" s="39" t="n"/>
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="6" t="n"/>
+      <c r="R14" s="6" t="n"/>
+      <c r="S14" s="6" t="n"/>
+      <c r="T14" s="6" t="n"/>
+      <c r="U14" s="6" t="n"/>
+      <c r="V14" s="6" t="n"/>
+      <c r="W14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>zkSync Era</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>zkSync Explorer</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D15" s="27" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>zkSync Era is an EVM-compatible ZK rollup developed by Matter Labs, using zero-knowledge proofs for secure and scalable Ethereum transactions with native account abstraction.</t>
         </is>
       </c>
-      <c r="E15" s="27" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>https://x.com/zksync</t>
         </is>
       </c>
-      <c r="F15" s="27" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>https://zksync.io</t>
         </is>
       </c>
-      <c r="G15" s="26" t="inlineStr">
+      <c r="G15" s="38" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H15" s="28" t="n"/>
-      <c r="I15" s="29" t="n"/>
-      <c r="J15" s="29" t="n"/>
-      <c r="K15" s="24" t="n"/>
-      <c r="L15" s="24" t="n"/>
-      <c r="M15" s="24" t="n"/>
-      <c r="N15" s="24" t="n"/>
-      <c r="O15" s="24" t="n"/>
-      <c r="P15" s="24" t="n"/>
-      <c r="Q15" s="24" t="n"/>
-      <c r="R15" s="24" t="n"/>
-      <c r="S15" s="24" t="n"/>
-      <c r="T15" s="24" t="n"/>
-      <c r="U15" s="24" t="n"/>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="24" t="n"/>
+      <c r="H15" s="39" t="n"/>
+      <c r="I15" s="39" t="n"/>
+      <c r="J15" s="39" t="n"/>
+      <c r="K15" s="16" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="6" t="n"/>
+      <c r="R15" s="6" t="n"/>
+      <c r="S15" s="6" t="n"/>
+      <c r="T15" s="6" t="n"/>
+      <c r="U15" s="6" t="n"/>
+      <c r="V15" s="6" t="n"/>
+      <c r="W15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Scroll</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Scrollscan</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>Scroll is a native zkEVM Layer-2 on Ethereum providing bytecode-level EVM equivalence using zero-knowledge proof verification for trustless and scalable transactions.</t>
         </is>
       </c>
-      <c r="E16" s="27" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>https://x.com/Scroll_ZKP</t>
         </is>
       </c>
-      <c r="F16" s="27" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr">
         <is>
           <t>https://scroll.io</t>
         </is>
       </c>
-      <c r="G16" s="26" t="inlineStr">
+      <c r="G16" s="38" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H16" s="28" t="n"/>
-      <c r="I16" s="29" t="n"/>
-      <c r="J16" s="29" t="n"/>
-      <c r="K16" s="24" t="n"/>
-      <c r="L16" s="24" t="n"/>
-      <c r="M16" s="24" t="n"/>
-      <c r="N16" s="24" t="n"/>
-      <c r="O16" s="24" t="n"/>
-      <c r="P16" s="24" t="n"/>
-      <c r="Q16" s="24" t="n"/>
-      <c r="R16" s="24" t="n"/>
-      <c r="S16" s="24" t="n"/>
-      <c r="T16" s="24" t="n"/>
-      <c r="U16" s="24" t="n"/>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="24" t="n"/>
+      <c r="H16" s="39" t="n"/>
+      <c r="I16" s="39" t="n"/>
+      <c r="J16" s="39" t="n"/>
+      <c r="K16" s="16" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="6" t="n"/>
+      <c r="R16" s="6" t="n"/>
+      <c r="S16" s="6" t="n"/>
+      <c r="T16" s="6" t="n"/>
+      <c r="U16" s="6" t="n"/>
+      <c r="V16" s="6" t="n"/>
+      <c r="W16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Linea</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Lineascan</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>Linea is an EVM-equivalent ZK rollup developed by ConsenSys, designed for seamless compatibility with Ethereum tooling while offering significantly reduced transaction costs.</t>
         </is>
       </c>
-      <c r="E17" s="27" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>https://x.com/LineaBuild</t>
         </is>
       </c>
-      <c r="F17" s="27" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>https://linea.build</t>
         </is>
       </c>
-      <c r="G17" s="27" t="inlineStr">
+      <c r="G17" s="40" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H17" s="28" t="n"/>
-      <c r="I17" s="25" t="n"/>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="24" t="n"/>
-      <c r="L17" s="24" t="n"/>
-      <c r="M17" s="24" t="n"/>
-      <c r="N17" s="24" t="n"/>
-      <c r="O17" s="24" t="n"/>
-      <c r="P17" s="24" t="n"/>
-      <c r="Q17" s="24" t="n"/>
-      <c r="R17" s="24" t="n"/>
-      <c r="S17" s="24" t="n"/>
-      <c r="T17" s="24" t="n"/>
-      <c r="U17" s="24" t="n"/>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="24" t="n"/>
+      <c r="H17" s="39" t="n"/>
+      <c r="I17" s="39" t="n"/>
+      <c r="J17" s="39" t="n"/>
+      <c r="K17" s="16" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="6" t="n"/>
+      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="6" t="n"/>
+      <c r="T17" s="6" t="n"/>
+      <c r="U17" s="6" t="n"/>
+      <c r="V17" s="6" t="n"/>
+      <c r="W17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>BNB Smart Chain</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>BscScan</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>OKLink</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>BNB Smart Chain is a high-performance EVM-compatible blockchain developed by Binance, supporting DeFi, NFTs, and Web3 applications with low transaction fees.</t>
         </is>
       </c>
-      <c r="E18" s="27" t="inlineStr">
+      <c r="E18" s="37" t="inlineStr">
         <is>
           <t>https://x.com/bnbchain</t>
         </is>
       </c>
-      <c r="F18" s="27" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>https://www.bnbchain.org</t>
         </is>
       </c>
-      <c r="G18" s="27" t="inlineStr">
+      <c r="G18" s="40" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="H18" s="28" t="n"/>
-      <c r="I18" s="29" t="n"/>
-      <c r="J18" s="29" t="n"/>
-      <c r="K18" s="24" t="n"/>
-      <c r="L18" s="24" t="n"/>
-      <c r="M18" s="24" t="n"/>
-      <c r="N18" s="24" t="n"/>
-      <c r="O18" s="24" t="n"/>
-      <c r="P18" s="24" t="n"/>
-      <c r="Q18" s="24" t="n"/>
-      <c r="R18" s="24" t="n"/>
-      <c r="S18" s="24" t="n"/>
-      <c r="T18" s="24" t="n"/>
-      <c r="U18" s="24" t="n"/>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="24" t="n"/>
+      <c r="H18" s="39" t="n"/>
+      <c r="I18" s="39" t="n"/>
+      <c r="J18" s="39" t="n"/>
+      <c r="K18" s="16" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="6" t="n"/>
+      <c r="R18" s="6" t="n"/>
+      <c r="S18" s="6" t="n"/>
+      <c r="T18" s="6" t="n"/>
+      <c r="U18" s="6" t="n"/>
+      <c r="V18" s="6" t="n"/>
+      <c r="W18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Tron</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>Tronscan</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>OKLink</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>TRON is a high-throughput Layer-1 blockchain focused on digital entertainment and content distribution, featuring a large DeFi ecosystem and the world's largest USDT circulation.</t>
         </is>
       </c>
-      <c r="E19" s="27" t="inlineStr">
+      <c r="E19" s="37" t="inlineStr">
         <is>
           <t>https://x.com/trondao</t>
         </is>
       </c>
-      <c r="F19" s="27" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>https://tron.network</t>
         </is>
       </c>
-      <c r="G19" s="26" t="inlineStr">
+      <c r="G19" s="38" t="inlineStr">
         <is>
           <t>TRON</t>
         </is>
       </c>
-      <c r="H19" s="28" t="n"/>
-      <c r="I19" s="29" t="n"/>
-      <c r="J19" s="29" t="n"/>
-      <c r="K19" s="24" t="n"/>
-      <c r="L19" s="24" t="n"/>
-      <c r="M19" s="24" t="n"/>
-      <c r="N19" s="24" t="n"/>
-      <c r="O19" s="24" t="n"/>
-      <c r="P19" s="24" t="n"/>
-      <c r="Q19" s="24" t="n"/>
-      <c r="R19" s="24" t="n"/>
-      <c r="S19" s="24" t="n"/>
-      <c r="T19" s="24" t="n"/>
-      <c r="U19" s="24" t="n"/>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="24" t="n"/>
+      <c r="H19" s="39" t="n"/>
+      <c r="I19" s="39" t="n"/>
+      <c r="J19" s="39" t="n"/>
+      <c r="K19" s="16" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="n"/>
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="6" t="n"/>
+      <c r="T19" s="6" t="n"/>
+      <c r="U19" s="6" t="n"/>
+      <c r="V19" s="6" t="n"/>
+      <c r="W19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Sonic</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>SonicScan</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>Routescan</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>Sonic is an EVM-compatible Layer-1 blockchain evolved from Fantom Opera, offering sub-second finality and a developer fee monetization program via Sonic Labs.</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="E20" s="37" t="inlineStr">
         <is>
           <t>https://x.com/SonicLabs</t>
         </is>
       </c>
-      <c r="F20" s="27" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>https://soniclabs.com</t>
         </is>
       </c>
-      <c r="G20" s="26" t="inlineStr">
+      <c r="G20" s="38" t="inlineStr">
         <is>
           <t>Sonic</t>
         </is>
       </c>
-      <c r="H20" s="28" t="n"/>
-      <c r="I20" s="29" t="n"/>
-      <c r="J20" s="29" t="n"/>
-      <c r="K20" s="24" t="n"/>
-      <c r="L20" s="24" t="n"/>
-      <c r="M20" s="24" t="n"/>
-      <c r="N20" s="24" t="n"/>
-      <c r="O20" s="24" t="n"/>
-      <c r="P20" s="24" t="n"/>
-      <c r="Q20" s="24" t="n"/>
-      <c r="R20" s="24" t="n"/>
-      <c r="S20" s="24" t="n"/>
-      <c r="T20" s="24" t="n"/>
-      <c r="U20" s="24" t="n"/>
-      <c r="V20" s="24" t="n"/>
-      <c r="W20" s="24" t="n"/>
+      <c r="H20" s="39" t="n"/>
+      <c r="I20" s="39" t="n"/>
+      <c r="J20" s="39" t="n"/>
+      <c r="K20" s="16" t="n"/>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
+      <c r="N20" s="6" t="n"/>
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="6" t="n"/>
+      <c r="Q20" s="6" t="n"/>
+      <c r="R20" s="6" t="n"/>
+      <c r="S20" s="6" t="n"/>
+      <c r="T20" s="6" t="n"/>
+      <c r="U20" s="6" t="n"/>
+      <c r="V20" s="6" t="n"/>
+      <c r="W20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Near Protocol</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>NearBlocks</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>NEAR Explorer</t>
         </is>
       </c>
-      <c r="D21" s="27" t="inlineStr">
+      <c r="D21" s="36" t="inlineStr">
         <is>
           <t>NEAR Protocol is a sharded, proof-of-stake Layer-1 blockchain designed for usability and scalability, featuring human-readable account names and low-cost smart contracts.</t>
         </is>
       </c>
-      <c r="E21" s="27" t="inlineStr">
+      <c r="E21" s="37" t="inlineStr">
         <is>
           <t>https://x.com/NEARProtocol</t>
         </is>
       </c>
-      <c r="F21" s="27" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>https://near.org</t>
         </is>
       </c>
-      <c r="G21" s="27" t="inlineStr">
+      <c r="G21" s="40" t="inlineStr">
         <is>
           <t>NEAR</t>
         </is>
       </c>
-      <c r="H21" s="28" t="n"/>
-      <c r="I21" s="29" t="n"/>
-      <c r="J21" s="29" t="n"/>
-      <c r="K21" s="24" t="n"/>
-      <c r="L21" s="24" t="n"/>
-      <c r="M21" s="24" t="n"/>
-      <c r="N21" s="24" t="n"/>
-      <c r="O21" s="24" t="n"/>
-      <c r="P21" s="24" t="n"/>
-      <c r="Q21" s="24" t="n"/>
-      <c r="R21" s="24" t="n"/>
-      <c r="S21" s="24" t="n"/>
-      <c r="T21" s="24" t="n"/>
-      <c r="U21" s="24" t="n"/>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="24" t="n"/>
+      <c r="H21" s="39" t="n"/>
+      <c r="I21" s="39" t="n"/>
+      <c r="J21" s="39" t="n"/>
+      <c r="K21" s="16" t="n"/>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="6" t="n"/>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="6" t="n"/>
+      <c r="R21" s="6" t="n"/>
+      <c r="S21" s="6" t="n"/>
+      <c r="T21" s="6" t="n"/>
+      <c r="U21" s="6" t="n"/>
+      <c r="V21" s="6" t="n"/>
+      <c r="W21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Algorand</t>
         </is>
       </c>
-      <c r="B22" s="27" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>Allo.info</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>Pera Explorer</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="D22" s="36" t="inlineStr">
         <is>
           <t>Algorand is a pure proof-of-stake Layer-1 blockchain offering instant transaction finality, carbon neutrality, and support for smart contracts and digital assets via AVM.</t>
         </is>
       </c>
-      <c r="E22" s="27" t="inlineStr">
+      <c r="E22" s="37" t="inlineStr">
         <is>
           <t>https://x.com/algorand</t>
         </is>
       </c>
-      <c r="F22" s="27" t="inlineStr">
+      <c r="F22" s="37" t="inlineStr">
         <is>
           <t>https://algorand.com</t>
         </is>
       </c>
-      <c r="G22" s="26" t="inlineStr">
+      <c r="G22" s="38" t="inlineStr">
         <is>
           <t>Algorand</t>
         </is>
       </c>
-      <c r="H22" s="28" t="n"/>
-      <c r="I22" s="29" t="n"/>
-      <c r="J22" s="29" t="n"/>
-      <c r="K22" s="24" t="n"/>
-      <c r="L22" s="24" t="n"/>
-      <c r="M22" s="24" t="n"/>
-      <c r="N22" s="24" t="n"/>
-      <c r="O22" s="24" t="n"/>
-      <c r="P22" s="24" t="n"/>
-      <c r="Q22" s="24" t="n"/>
-      <c r="R22" s="24" t="n"/>
-      <c r="S22" s="24" t="n"/>
-      <c r="T22" s="24" t="n"/>
-      <c r="U22" s="24" t="n"/>
-      <c r="V22" s="24" t="n"/>
-      <c r="W22" s="24" t="n"/>
+      <c r="H22" s="39" t="n"/>
+      <c r="I22" s="39" t="n"/>
+      <c r="J22" s="39" t="n"/>
+      <c r="K22" s="16" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="6" t="n"/>
+      <c r="R22" s="6" t="n"/>
+      <c r="S22" s="6" t="n"/>
+      <c r="T22" s="6" t="n"/>
+      <c r="U22" s="6" t="n"/>
+      <c r="V22" s="6" t="n"/>
+      <c r="W22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Cosmos Hub</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Mintscan</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>Big Dipper</t>
         </is>
       </c>
-      <c r="D23" s="27" t="inlineStr">
+      <c r="D23" s="36" t="inlineStr">
         <is>
           <t>Cosmos Hub is the central blockchain of the Cosmos ecosystem, enabling inter-blockchain communication (IBC) between sovereign chains and serving as the network's main security hub.</t>
         </is>
       </c>
-      <c r="E23" s="27" t="inlineStr">
+      <c r="E23" s="37" t="inlineStr">
         <is>
           <t>https://x.com/cosmos</t>
         </is>
       </c>
-      <c r="F23" s="27" t="inlineStr">
+      <c r="F23" s="37" t="inlineStr">
         <is>
           <t>https://cosmos.network</t>
         </is>
       </c>
-      <c r="G23" s="27" t="inlineStr">
+      <c r="G23" s="40" t="inlineStr">
         <is>
           <t>Cosmos</t>
         </is>
       </c>
-      <c r="H23" s="28" t="n"/>
-      <c r="I23" s="29" t="n"/>
-      <c r="J23" s="29" t="n"/>
-      <c r="K23" s="24" t="n"/>
-      <c r="L23" s="24" t="n"/>
-      <c r="M23" s="24" t="n"/>
-      <c r="N23" s="24" t="n"/>
-      <c r="O23" s="24" t="n"/>
-      <c r="P23" s="24" t="n"/>
-      <c r="Q23" s="24" t="n"/>
-      <c r="R23" s="24" t="n"/>
-      <c r="S23" s="24" t="n"/>
-      <c r="T23" s="24" t="n"/>
-      <c r="U23" s="24" t="n"/>
-      <c r="V23" s="24" t="n"/>
-      <c r="W23" s="24" t="n"/>
+      <c r="H23" s="39" t="n"/>
+      <c r="I23" s="39" t="n"/>
+      <c r="J23" s="39" t="n"/>
+      <c r="K23" s="16" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n"/>
+      <c r="Q23" s="6" t="n"/>
+      <c r="R23" s="6" t="n"/>
+      <c r="S23" s="6" t="n"/>
+      <c r="T23" s="6" t="n"/>
+      <c r="U23" s="6" t="n"/>
+      <c r="V23" s="6" t="n"/>
+      <c r="W23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>Polkadot</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Subscan</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>Polkascan</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>Polkadot is a multichain network developed by Parity Technologies enabling interoperability between specialized blockchains called parachains via a central Relay Chain.</t>
         </is>
       </c>
-      <c r="E24" s="27" t="inlineStr">
+      <c r="E24" s="37" t="inlineStr">
         <is>
           <t>https://x.com/polkadot</t>
         </is>
       </c>
-      <c r="F24" s="27" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>https://polkadot.network</t>
         </is>
       </c>
-      <c r="G24" s="26" t="inlineStr">
+      <c r="G24" s="38" t="inlineStr">
         <is>
           <t>Polkadot</t>
         </is>
       </c>
-      <c r="H24" s="28" t="n"/>
-      <c r="I24" s="29" t="n"/>
-      <c r="J24" s="29" t="n"/>
-      <c r="K24" s="24" t="n"/>
-      <c r="L24" s="24" t="n"/>
-      <c r="M24" s="24" t="n"/>
-      <c r="N24" s="24" t="n"/>
-      <c r="O24" s="24" t="n"/>
-      <c r="P24" s="24" t="n"/>
-      <c r="Q24" s="24" t="n"/>
-      <c r="R24" s="24" t="n"/>
-      <c r="S24" s="24" t="n"/>
-      <c r="T24" s="24" t="n"/>
-      <c r="U24" s="24" t="n"/>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="24" t="n"/>
+      <c r="H24" s="39" t="n"/>
+      <c r="I24" s="39" t="n"/>
+      <c r="J24" s="39" t="n"/>
+      <c r="K24" s="16" t="n"/>
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
+      <c r="N24" s="6" t="n"/>
+      <c r="O24" s="6" t="n"/>
+      <c r="P24" s="6" t="n"/>
+      <c r="Q24" s="6" t="n"/>
+      <c r="R24" s="6" t="n"/>
+      <c r="S24" s="6" t="n"/>
+      <c r="T24" s="6" t="n"/>
+      <c r="U24" s="6" t="n"/>
+      <c r="V24" s="6" t="n"/>
+      <c r="W24" s="6" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>Stellar</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Stellar Expert</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>StellarChain</t>
         </is>
       </c>
-      <c r="D25" s="27" t="inlineStr">
+      <c r="D25" s="36" t="inlineStr">
         <is>
           <t>Stellar is an open-source payment network designed for fast, affordable cross-border transactions and digital asset issuance, widely adopted by financial institutions globally.</t>
         </is>
       </c>
-      <c r="E25" s="27" t="inlineStr">
+      <c r="E25" s="37" t="inlineStr">
         <is>
           <t>https://x.com/StellarOrg</t>
         </is>
       </c>
-      <c r="F25" s="27" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr">
         <is>
           <t>https://stellar.org</t>
         </is>
       </c>
-      <c r="G25" s="27" t="inlineStr">
+      <c r="G25" s="40" t="inlineStr">
         <is>
           <t>Lumen</t>
         </is>
       </c>
-      <c r="H25" s="28" t="n"/>
-      <c r="I25" s="29" t="n"/>
-      <c r="J25" s="29" t="n"/>
-      <c r="K25" s="24" t="n"/>
-      <c r="L25" s="24" t="n"/>
-      <c r="M25" s="24" t="n"/>
-      <c r="N25" s="24" t="n"/>
-      <c r="O25" s="24" t="n"/>
-      <c r="P25" s="24" t="n"/>
-      <c r="Q25" s="24" t="n"/>
-      <c r="R25" s="24" t="n"/>
-      <c r="S25" s="24" t="n"/>
-      <c r="T25" s="24" t="n"/>
-      <c r="U25" s="24" t="n"/>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="24" t="n"/>
+      <c r="H25" s="39" t="n"/>
+      <c r="I25" s="39" t="n"/>
+      <c r="J25" s="39" t="n"/>
+      <c r="K25" s="16" t="n"/>
+      <c r="L25" s="6" t="n"/>
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="6" t="n"/>
+      <c r="P25" s="6" t="n"/>
+      <c r="Q25" s="6" t="n"/>
+      <c r="R25" s="6" t="n"/>
+      <c r="S25" s="6" t="n"/>
+      <c r="T25" s="6" t="n"/>
+      <c r="U25" s="6" t="n"/>
+      <c r="V25" s="6" t="n"/>
+      <c r="W25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>Tezos</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>TzKT</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C26" s="35" t="inlineStr">
         <is>
           <t>Better Call Dev</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="D26" s="36" t="inlineStr">
         <is>
           <t>Tezos is a self-amending Layer-1 blockchain using liquid proof-of-stake, featuring on-chain governance and formal verification of smart contracts written in Michelson.</t>
         </is>
       </c>
-      <c r="E26" s="27" t="inlineStr">
+      <c r="E26" s="37" t="inlineStr">
         <is>
           <t>https://x.com/tezos</t>
         </is>
       </c>
-      <c r="F26" s="27" t="inlineStr">
+      <c r="F26" s="37" t="inlineStr">
         <is>
           <t>https://tezos.com</t>
         </is>
       </c>
-      <c r="G26" s="26" t="inlineStr">
+      <c r="G26" s="38" t="inlineStr">
         <is>
           <t>Tezos</t>
         </is>
       </c>
-      <c r="H26" s="28" t="n"/>
-      <c r="I26" s="25" t="n"/>
-      <c r="J26" s="25" t="n"/>
-      <c r="K26" s="24" t="n"/>
-      <c r="L26" s="24" t="n"/>
-      <c r="M26" s="24" t="n"/>
-      <c r="N26" s="24" t="n"/>
-      <c r="O26" s="24" t="n"/>
-      <c r="P26" s="24" t="n"/>
-      <c r="Q26" s="24" t="n"/>
-      <c r="R26" s="24" t="n"/>
-      <c r="S26" s="24" t="n"/>
-      <c r="T26" s="24" t="n"/>
-      <c r="U26" s="24" t="n"/>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="24" t="n"/>
+      <c r="H26" s="39" t="n"/>
+      <c r="I26" s="39" t="n"/>
+      <c r="J26" s="39" t="n"/>
+      <c r="K26" s="16" t="n"/>
+      <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
+      <c r="N26" s="6" t="n"/>
+      <c r="O26" s="6" t="n"/>
+      <c r="P26" s="6" t="n"/>
+      <c r="Q26" s="6" t="n"/>
+      <c r="R26" s="6" t="n"/>
+      <c r="S26" s="6" t="n"/>
+      <c r="T26" s="6" t="n"/>
+      <c r="U26" s="6" t="n"/>
+      <c r="V26" s="6" t="n"/>
+      <c r="W26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>Hedera</t>
         </is>
       </c>
-      <c r="B27" s="26" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>HashScan</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C27" s="35" t="inlineStr">
         <is>
           <t>DragonGlass</t>
         </is>
       </c>
-      <c r="D27" s="27" t="inlineStr">
+      <c r="D27" s="36" t="inlineStr">
         <is>
           <t>Hedera is a public distributed ledger using hashgraph consensus, offering high-throughput, low-latency transactions governed by a council of leading global enterprises.</t>
         </is>
       </c>
-      <c r="E27" s="27" t="inlineStr">
+      <c r="E27" s="37" t="inlineStr">
         <is>
           <t>https://x.com/hedera</t>
         </is>
       </c>
-      <c r="F27" s="27" t="inlineStr">
+      <c r="F27" s="37" t="inlineStr">
         <is>
           <t>https://hedera.com</t>
         </is>
       </c>
-      <c r="G27" s="26" t="inlineStr">
+      <c r="G27" s="38" t="inlineStr">
         <is>
           <t>Hedera</t>
         </is>
       </c>
-      <c r="H27" s="28" t="n"/>
-      <c r="I27" s="29" t="n"/>
-      <c r="J27" s="29" t="n"/>
-      <c r="K27" s="24" t="n"/>
-      <c r="L27" s="24" t="n"/>
-      <c r="M27" s="24" t="n"/>
-      <c r="N27" s="24" t="n"/>
-      <c r="O27" s="24" t="n"/>
-      <c r="P27" s="24" t="n"/>
-      <c r="Q27" s="24" t="n"/>
-      <c r="R27" s="24" t="n"/>
-      <c r="S27" s="24" t="n"/>
-      <c r="T27" s="24" t="n"/>
-      <c r="U27" s="24" t="n"/>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="24" t="n"/>
+      <c r="H27" s="39" t="n"/>
+      <c r="I27" s="39" t="n"/>
+      <c r="J27" s="39" t="n"/>
+      <c r="K27" s="16" t="n"/>
+      <c r="L27" s="6" t="n"/>
+      <c r="M27" s="6" t="n"/>
+      <c r="N27" s="6" t="n"/>
+      <c r="O27" s="6" t="n"/>
+      <c r="P27" s="6" t="n"/>
+      <c r="Q27" s="6" t="n"/>
+      <c r="R27" s="6" t="n"/>
+      <c r="S27" s="6" t="n"/>
+      <c r="T27" s="6" t="n"/>
+      <c r="U27" s="6" t="n"/>
+      <c r="V27" s="6" t="n"/>
+      <c r="W27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>Aptos</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>Aptos Explorer</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C28" s="35" t="inlineStr">
         <is>
           <t>AptScan</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>Aptos is a Layer-1 blockchain developed by former Meta engineers using the Move programming language, featuring parallel transaction execution for high throughput and safety.</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr">
+      <c r="E28" s="37" t="inlineStr">
         <is>
           <t>https://x.com/aptos_network</t>
         </is>
       </c>
-      <c r="F28" s="27" t="inlineStr">
+      <c r="F28" s="37" t="inlineStr">
         <is>
           <t>https://aptoslabs.com</t>
         </is>
       </c>
-      <c r="G28" s="26" t="inlineStr">
+      <c r="G28" s="38" t="inlineStr">
         <is>
           <t>Aptos</t>
         </is>
       </c>
-      <c r="H28" s="28" t="n"/>
-      <c r="I28" s="29" t="n"/>
-      <c r="J28" s="29" t="n"/>
-      <c r="K28" s="24" t="n"/>
-      <c r="L28" s="24" t="n"/>
-      <c r="M28" s="24" t="n"/>
-      <c r="N28" s="24" t="n"/>
-      <c r="O28" s="24" t="n"/>
-      <c r="P28" s="24" t="n"/>
-      <c r="Q28" s="24" t="n"/>
-      <c r="R28" s="24" t="n"/>
-      <c r="S28" s="24" t="n"/>
-      <c r="T28" s="24" t="n"/>
-      <c r="U28" s="24" t="n"/>
-      <c r="V28" s="24" t="n"/>
-      <c r="W28" s="24" t="n"/>
+      <c r="H28" s="39" t="n"/>
+      <c r="I28" s="39" t="n"/>
+      <c r="J28" s="39" t="n"/>
+      <c r="K28" s="16" t="n"/>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
+      <c r="N28" s="6" t="n"/>
+      <c r="O28" s="6" t="n"/>
+      <c r="P28" s="6" t="n"/>
+      <c r="Q28" s="6" t="n"/>
+      <c r="R28" s="6" t="n"/>
+      <c r="S28" s="6" t="n"/>
+      <c r="T28" s="6" t="n"/>
+      <c r="U28" s="6" t="n"/>
+      <c r="V28" s="6" t="n"/>
+      <c r="W28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t>Sui</t>
         </is>
       </c>
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>SuiVision</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C29" s="35" t="inlineStr">
         <is>
           <t>SuiScan</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="D29" s="36" t="inlineStr">
         <is>
           <t>Sui is a Layer-1 blockchain developed by Mysten Labs using the Move language, featuring an object-centric data model and parallel transaction processing for high performance.</t>
         </is>
       </c>
-      <c r="E29" s="27" t="inlineStr">
+      <c r="E29" s="37" t="inlineStr">
         <is>
           <t>https://x.com/SuiNetwork</t>
         </is>
       </c>
-      <c r="F29" s="27" t="inlineStr">
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>https://sui.io</t>
         </is>
       </c>
-      <c r="G29" s="27" t="inlineStr">
+      <c r="G29" s="40" t="inlineStr">
         <is>
           <t>Sui</t>
         </is>
       </c>
-      <c r="H29" s="28" t="n"/>
-      <c r="I29" s="29" t="n"/>
-      <c r="J29" s="29" t="n"/>
-      <c r="K29" s="24" t="n"/>
-      <c r="L29" s="24" t="n"/>
-      <c r="M29" s="24" t="n"/>
-      <c r="N29" s="24" t="n"/>
-      <c r="O29" s="24" t="n"/>
-      <c r="P29" s="24" t="n"/>
-      <c r="Q29" s="24" t="n"/>
-      <c r="R29" s="24" t="n"/>
-      <c r="S29" s="24" t="n"/>
-      <c r="T29" s="24" t="n"/>
-      <c r="U29" s="24" t="n"/>
-      <c r="V29" s="24" t="n"/>
-      <c r="W29" s="24" t="n"/>
+      <c r="H29" s="39" t="n"/>
+      <c r="I29" s="39" t="n"/>
+      <c r="J29" s="39" t="n"/>
+      <c r="K29" s="16" t="n"/>
+      <c r="L29" s="6" t="n"/>
+      <c r="M29" s="6" t="n"/>
+      <c r="N29" s="6" t="n"/>
+      <c r="O29" s="6" t="n"/>
+      <c r="P29" s="6" t="n"/>
+      <c r="Q29" s="6" t="n"/>
+      <c r="R29" s="6" t="n"/>
+      <c r="S29" s="6" t="n"/>
+      <c r="T29" s="6" t="n"/>
+      <c r="U29" s="6" t="n"/>
+      <c r="V29" s="6" t="n"/>
+      <c r="W29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>Sei</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>Seitrace</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="35" t="inlineStr">
         <is>
           <t>SeiScan</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="D30" s="36" t="inlineStr">
         <is>
           <t>Sei is a Layer-1 blockchain optimized for trading applications, featuring parallelized EVM execution, twin-turbo consensus, and native order book primitives in the protocol.</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr">
+      <c r="E30" s="37" t="inlineStr">
         <is>
           <t>https://x.com/SeiNetwork</t>
         </is>
       </c>
-      <c r="F30" s="27" t="inlineStr">
+      <c r="F30" s="37" t="inlineStr">
         <is>
           <t>https://sei.io</t>
         </is>
       </c>
-      <c r="G30" s="26" t="inlineStr">
+      <c r="G30" s="38" t="inlineStr">
         <is>
           <t>Sei</t>
         </is>
       </c>
-      <c r="H30" s="28" t="n"/>
-      <c r="I30" s="29" t="n"/>
-      <c r="J30" s="29" t="n"/>
-      <c r="K30" s="24" t="n"/>
-      <c r="L30" s="24" t="n"/>
-      <c r="M30" s="24" t="n"/>
-      <c r="N30" s="24" t="n"/>
-      <c r="O30" s="24" t="n"/>
-      <c r="P30" s="24" t="n"/>
-      <c r="Q30" s="24" t="n"/>
-      <c r="R30" s="24" t="n"/>
-      <c r="S30" s="24" t="n"/>
-      <c r="T30" s="24" t="n"/>
-      <c r="U30" s="24" t="n"/>
-      <c r="V30" s="24" t="n"/>
-      <c r="W30" s="24" t="n"/>
+      <c r="H30" s="39" t="n"/>
+      <c r="I30" s="39" t="n"/>
+      <c r="J30" s="39" t="n"/>
+      <c r="K30" s="16" t="n"/>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="n"/>
+      <c r="N30" s="6" t="n"/>
+      <c r="O30" s="6" t="n"/>
+      <c r="P30" s="6" t="n"/>
+      <c r="Q30" s="6" t="n"/>
+      <c r="R30" s="6" t="n"/>
+      <c r="S30" s="6" t="n"/>
+      <c r="T30" s="6" t="n"/>
+      <c r="U30" s="6" t="n"/>
+      <c r="V30" s="6" t="n"/>
+      <c r="W30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>Kaia</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Kaiascan</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C31" s="35" t="inlineStr">
         <is>
           <t>OKLink</t>
         </is>
       </c>
-      <c r="D31" s="27" t="inlineStr">
+      <c r="D31" s="36" t="inlineStr">
         <is>
           <t>Kaia (formerly Klaytn) is an EVM-compatible Layer-1 blockchain developed by the Kaia DLT Foundation, focusing on Web3 accessibility and enterprise adoption in Asia.</t>
         </is>
       </c>
-      <c r="E31" s="27" t="inlineStr">
+      <c r="E31" s="37" t="inlineStr">
         <is>
           <t>https://x.com/KaiaChain</t>
         </is>
       </c>
-      <c r="F31" s="27" t="inlineStr">
+      <c r="F31" s="37" t="inlineStr">
         <is>
           <t>https://kaia.io</t>
         </is>
       </c>
-      <c r="G31" s="26" t="inlineStr">
+      <c r="G31" s="38" t="inlineStr">
         <is>
           <t>Kaia</t>
         </is>
       </c>
-      <c r="H31" s="28" t="n"/>
-      <c r="I31" s="29" t="n"/>
-      <c r="J31" s="25" t="n"/>
-      <c r="K31" s="24" t="n"/>
-      <c r="L31" s="24" t="n"/>
-      <c r="M31" s="24" t="n"/>
-      <c r="N31" s="24" t="n"/>
-      <c r="O31" s="24" t="n"/>
-      <c r="P31" s="24" t="n"/>
-      <c r="Q31" s="24" t="n"/>
-      <c r="R31" s="24" t="n"/>
-      <c r="S31" s="24" t="n"/>
-      <c r="T31" s="24" t="n"/>
-      <c r="U31" s="24" t="n"/>
-      <c r="V31" s="24" t="n"/>
-      <c r="W31" s="24" t="n"/>
+      <c r="H31" s="39" t="n"/>
+      <c r="I31" s="39" t="n"/>
+      <c r="J31" s="39" t="n"/>
+      <c r="K31" s="16" t="n"/>
+      <c r="L31" s="6" t="n"/>
+      <c r="M31" s="6" t="n"/>
+      <c r="N31" s="6" t="n"/>
+      <c r="O31" s="6" t="n"/>
+      <c r="P31" s="6" t="n"/>
+      <c r="Q31" s="6" t="n"/>
+      <c r="R31" s="6" t="n"/>
+      <c r="S31" s="6" t="n"/>
+      <c r="T31" s="6" t="n"/>
+      <c r="U31" s="6" t="n"/>
+      <c r="V31" s="6" t="n"/>
+      <c r="W31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>Harmony Explorer</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D32" s="27" t="inlineStr">
+      <c r="D32" s="36" t="inlineStr">
         <is>
           <t>Harmony is a sharded proof-of-stake Layer-1 blockchain focused on cross-chain bridging and decentralized applications, using effective proof-of-stake for fast finality.</t>
         </is>
       </c>
-      <c r="E32" s="27" t="inlineStr">
+      <c r="E32" s="37" t="inlineStr">
         <is>
           <t>https://x.com/harmonyprotocol</t>
         </is>
       </c>
-      <c r="F32" s="27" t="inlineStr">
+      <c r="F32" s="37" t="inlineStr">
         <is>
           <t>https://harmony.one</t>
         </is>
       </c>
-      <c r="G32" s="27" t="inlineStr">
+      <c r="G32" s="40" t="inlineStr">
         <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="H32" s="28" t="n"/>
-      <c r="I32" s="29" t="n"/>
-      <c r="J32" s="29" t="n"/>
-      <c r="K32" s="24" t="n"/>
-      <c r="L32" s="24" t="n"/>
-      <c r="M32" s="24" t="n"/>
-      <c r="N32" s="24" t="n"/>
-      <c r="O32" s="24" t="n"/>
-      <c r="P32" s="24" t="n"/>
-      <c r="Q32" s="24" t="n"/>
-      <c r="R32" s="24" t="n"/>
-      <c r="S32" s="24" t="n"/>
-      <c r="T32" s="24" t="n"/>
-      <c r="U32" s="24" t="n"/>
-      <c r="V32" s="24" t="n"/>
-      <c r="W32" s="24" t="n"/>
+      <c r="H32" s="39" t="n"/>
+      <c r="I32" s="39" t="n"/>
+      <c r="J32" s="39" t="n"/>
+      <c r="K32" s="16" t="n"/>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="n"/>
+      <c r="N32" s="6" t="n"/>
+      <c r="O32" s="6" t="n"/>
+      <c r="P32" s="6" t="n"/>
+      <c r="Q32" s="6" t="n"/>
+      <c r="R32" s="6" t="n"/>
+      <c r="S32" s="6" t="n"/>
+      <c r="T32" s="6" t="n"/>
+      <c r="U32" s="6" t="n"/>
+      <c r="V32" s="6" t="n"/>
+      <c r="W32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="34" t="inlineStr">
         <is>
           <t>Arbitrum One</t>
         </is>
       </c>
-      <c r="B33" s="26" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>Arbiscan</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C33" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D33" s="27" t="inlineStr">
+      <c r="D33" s="36" t="inlineStr">
         <is>
           <t>Arbitrum One is an Ethereum Layer-2 optimistic rollup developed by Offchain Labs, delivering high throughput and low fees with full EVM compatibility.</t>
         </is>
       </c>
-      <c r="E33" s="27" t="inlineStr">
+      <c r="E33" s="37" t="inlineStr">
         <is>
           <t>https://x.com/arbitrum</t>
         </is>
       </c>
-      <c r="F33" s="27" t="inlineStr">
+      <c r="F33" s="37" t="inlineStr">
         <is>
           <t>https://arbitrum.io</t>
         </is>
       </c>
-      <c r="G33" s="27" t="inlineStr">
+      <c r="G33" s="40" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H33" s="28" t="n"/>
-      <c r="I33" s="29" t="n"/>
-      <c r="J33" s="29" t="n"/>
-      <c r="K33" s="24" t="n"/>
-      <c r="L33" s="24" t="n"/>
-      <c r="M33" s="24" t="n"/>
-      <c r="N33" s="24" t="n"/>
-      <c r="O33" s="24" t="n"/>
-      <c r="P33" s="24" t="n"/>
-      <c r="Q33" s="24" t="n"/>
-      <c r="R33" s="24" t="n"/>
-      <c r="S33" s="24" t="n"/>
-      <c r="T33" s="24" t="n"/>
-      <c r="U33" s="24" t="n"/>
-      <c r="V33" s="24" t="n"/>
-      <c r="W33" s="24" t="n"/>
+      <c r="H33" s="39" t="n"/>
+      <c r="I33" s="39" t="n"/>
+      <c r="J33" s="39" t="n"/>
+      <c r="K33" s="16" t="n"/>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="6" t="n"/>
+      <c r="N33" s="6" t="n"/>
+      <c r="O33" s="6" t="n"/>
+      <c r="P33" s="6" t="n"/>
+      <c r="Q33" s="6" t="n"/>
+      <c r="R33" s="6" t="n"/>
+      <c r="S33" s="6" t="n"/>
+      <c r="T33" s="6" t="n"/>
+      <c r="U33" s="6" t="n"/>
+      <c r="V33" s="6" t="n"/>
+      <c r="W33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t>Optimism</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>Optimistic Etherscan</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C34" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D34" s="27" t="inlineStr">
+      <c r="D34" s="36" t="inlineStr">
         <is>
           <t>Optimism is an Ethereum Layer-2 optimistic rollup providing EVM-equivalent scalability with a fraud-proof security model, governed by the Optimism Collective.</t>
         </is>
       </c>
-      <c r="E34" s="27" t="inlineStr">
+      <c r="E34" s="37" t="inlineStr">
         <is>
           <t>https://x.com/optimismFND</t>
         </is>
       </c>
-      <c r="F34" s="27" t="inlineStr">
+      <c r="F34" s="37" t="inlineStr">
         <is>
           <t>https://optimism.io</t>
         </is>
       </c>
-      <c r="G34" s="27" t="inlineStr">
+      <c r="G34" s="40" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H34" s="28" t="n"/>
-      <c r="I34" s="29" t="n"/>
-      <c r="J34" s="29" t="n"/>
-      <c r="K34" s="24" t="n"/>
-      <c r="L34" s="24" t="n"/>
-      <c r="M34" s="24" t="n"/>
-      <c r="N34" s="24" t="n"/>
-      <c r="O34" s="24" t="n"/>
-      <c r="P34" s="24" t="n"/>
-      <c r="Q34" s="24" t="n"/>
-      <c r="R34" s="24" t="n"/>
-      <c r="S34" s="24" t="n"/>
-      <c r="T34" s="24" t="n"/>
-      <c r="U34" s="24" t="n"/>
-      <c r="V34" s="24" t="n"/>
-      <c r="W34" s="24" t="n"/>
+      <c r="H34" s="39" t="n"/>
+      <c r="I34" s="39" t="n"/>
+      <c r="J34" s="39" t="n"/>
+      <c r="K34" s="16" t="n"/>
+      <c r="L34" s="6" t="n"/>
+      <c r="M34" s="6" t="n"/>
+      <c r="N34" s="6" t="n"/>
+      <c r="O34" s="6" t="n"/>
+      <c r="P34" s="6" t="n"/>
+      <c r="Q34" s="6" t="n"/>
+      <c r="R34" s="6" t="n"/>
+      <c r="S34" s="6" t="n"/>
+      <c r="T34" s="6" t="n"/>
+      <c r="U34" s="6" t="n"/>
+      <c r="V34" s="6" t="n"/>
+      <c r="W34" s="6" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="25" t="inlineStr">
+      <c r="A35" s="34" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="B35" s="26" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>BaseScan</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="C35" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D35" s="27" t="inlineStr">
+      <c r="D35" s="36" t="inlineStr">
         <is>
           <t>Base is an Ethereum Layer-2 network built by Coinbase using the OP Stack, offering low-cost EVM-compatible transactions with seamless access to Coinbase's ecosystem.</t>
         </is>
       </c>
-      <c r="E35" s="27" t="inlineStr">
+      <c r="E35" s="37" t="inlineStr">
         <is>
           <t>https://x.com/base</t>
         </is>
       </c>
-      <c r="F35" s="27" t="inlineStr">
+      <c r="F35" s="37" t="inlineStr">
         <is>
           <t>https://base.org</t>
         </is>
       </c>
-      <c r="G35" s="27" t="inlineStr">
+      <c r="G35" s="40" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H35" s="28" t="n"/>
-      <c r="I35" s="29" t="n"/>
-      <c r="J35" s="29" t="n"/>
-      <c r="K35" s="24" t="n"/>
-      <c r="L35" s="24" t="n"/>
-      <c r="M35" s="24" t="n"/>
-      <c r="N35" s="24" t="n"/>
-      <c r="O35" s="24" t="n"/>
-      <c r="P35" s="24" t="n"/>
-      <c r="Q35" s="24" t="n"/>
-      <c r="R35" s="24" t="n"/>
-      <c r="S35" s="24" t="n"/>
-      <c r="T35" s="24" t="n"/>
-      <c r="U35" s="24" t="n"/>
-      <c r="V35" s="24" t="n"/>
-      <c r="W35" s="24" t="n"/>
+      <c r="H35" s="39" t="n"/>
+      <c r="I35" s="39" t="n"/>
+      <c r="J35" s="39" t="n"/>
+      <c r="K35" s="16" t="n"/>
+      <c r="L35" s="6" t="n"/>
+      <c r="M35" s="6" t="n"/>
+      <c r="N35" s="6" t="n"/>
+      <c r="O35" s="6" t="n"/>
+      <c r="P35" s="6" t="n"/>
+      <c r="Q35" s="6" t="n"/>
+      <c r="R35" s="6" t="n"/>
+      <c r="S35" s="6" t="n"/>
+      <c r="T35" s="6" t="n"/>
+      <c r="U35" s="6" t="n"/>
+      <c r="V35" s="6" t="n"/>
+      <c r="W35" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="25" t="inlineStr">
+      <c r="A36" s="34" t="inlineStr">
         <is>
           <t>Blast</t>
         </is>
       </c>
-      <c r="B36" s="26" t="inlineStr">
+      <c r="B36" s="35" t="inlineStr">
         <is>
           <t>Blastscan</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C36" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D36" s="27" t="inlineStr">
+      <c r="D36" s="36" t="inlineStr">
         <is>
           <t>Blast is an Ethereum Layer-2 optimistic rollup offering native yield for ETH and stablecoins through automatic rebasing, built by the team behind the Blur NFT marketplace.</t>
         </is>
       </c>
-      <c r="E36" s="27" t="inlineStr">
+      <c r="E36" s="37" t="inlineStr">
         <is>
           <t>https://x.com/Blast_L2</t>
         </is>
       </c>
-      <c r="F36" s="27" t="inlineStr">
+      <c r="F36" s="37" t="inlineStr">
         <is>
           <t>https://blast.io</t>
         </is>
       </c>
-      <c r="G36" s="26" t="inlineStr">
+      <c r="G36" s="38" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H36" s="28" t="n"/>
-      <c r="I36" s="29" t="n"/>
-      <c r="J36" s="25" t="n"/>
-      <c r="K36" s="24" t="n"/>
-      <c r="L36" s="24" t="n"/>
-      <c r="M36" s="24" t="n"/>
-      <c r="N36" s="24" t="n"/>
-      <c r="O36" s="24" t="n"/>
-      <c r="P36" s="24" t="n"/>
-      <c r="Q36" s="24" t="n"/>
-      <c r="R36" s="24" t="n"/>
-      <c r="S36" s="24" t="n"/>
-      <c r="T36" s="24" t="n"/>
-      <c r="U36" s="24" t="n"/>
-      <c r="V36" s="24" t="n"/>
-      <c r="W36" s="24" t="n"/>
+      <c r="H36" s="39" t="n"/>
+      <c r="I36" s="39" t="n"/>
+      <c r="J36" s="39" t="n"/>
+      <c r="K36" s="16" t="n"/>
+      <c r="L36" s="6" t="n"/>
+      <c r="M36" s="6" t="n"/>
+      <c r="N36" s="6" t="n"/>
+      <c r="O36" s="6" t="n"/>
+      <c r="P36" s="6" t="n"/>
+      <c r="Q36" s="6" t="n"/>
+      <c r="R36" s="6" t="n"/>
+      <c r="S36" s="6" t="n"/>
+      <c r="T36" s="6" t="n"/>
+      <c r="U36" s="6" t="n"/>
+      <c r="V36" s="6" t="n"/>
+      <c r="W36" s="6" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="A37" s="34" t="inlineStr">
         <is>
           <t>Mantle</t>
         </is>
       </c>
-      <c r="B37" s="26" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>MantleScan</t>
         </is>
       </c>
-      <c r="C37" s="26" t="inlineStr">
+      <c r="C37" s="35" t="inlineStr">
         <is>
           <t>Mantle Explorer</t>
         </is>
       </c>
-      <c r="D37" s="27" t="inlineStr">
+      <c r="D37" s="36" t="inlineStr">
         <is>
           <t>Mantle is an Ethereum Layer-2 network using optimistic rollup technology with modular data availability via EigenDA, using MNT as its native gas token.</t>
         </is>
       </c>
-      <c r="E37" s="27" t="inlineStr">
+      <c r="E37" s="37" t="inlineStr">
         <is>
           <t>https://x.com/0xMantle</t>
         </is>
       </c>
-      <c r="F37" s="27" t="inlineStr">
+      <c r="F37" s="37" t="inlineStr">
         <is>
           <t>https://mantle.xyz</t>
         </is>
       </c>
-      <c r="G37" s="26" t="inlineStr">
+      <c r="G37" s="38" t="inlineStr">
         <is>
           <t>Mantle</t>
         </is>
       </c>
-      <c r="H37" s="28" t="n"/>
-      <c r="I37" s="29" t="n"/>
-      <c r="J37" s="29" t="n"/>
-      <c r="K37" s="24" t="n"/>
-      <c r="L37" s="24" t="n"/>
-      <c r="M37" s="24" t="n"/>
-      <c r="N37" s="24" t="n"/>
-      <c r="O37" s="24" t="n"/>
-      <c r="P37" s="24" t="n"/>
-      <c r="Q37" s="24" t="n"/>
-      <c r="R37" s="24" t="n"/>
-      <c r="S37" s="24" t="n"/>
-      <c r="T37" s="24" t="n"/>
-      <c r="U37" s="24" t="n"/>
-      <c r="V37" s="24" t="n"/>
-      <c r="W37" s="24" t="n"/>
+      <c r="H37" s="39" t="n"/>
+      <c r="I37" s="39" t="n"/>
+      <c r="J37" s="39" t="n"/>
+      <c r="K37" s="16" t="n"/>
+      <c r="L37" s="6" t="n"/>
+      <c r="M37" s="6" t="n"/>
+      <c r="N37" s="6" t="n"/>
+      <c r="O37" s="6" t="n"/>
+      <c r="P37" s="6" t="n"/>
+      <c r="Q37" s="6" t="n"/>
+      <c r="R37" s="6" t="n"/>
+      <c r="S37" s="6" t="n"/>
+      <c r="T37" s="6" t="n"/>
+      <c r="U37" s="6" t="n"/>
+      <c r="V37" s="6" t="n"/>
+      <c r="W37" s="6" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="25" t="inlineStr">
+      <c r="A38" s="34" t="inlineStr">
         <is>
           <t>Metis</t>
         </is>
       </c>
-      <c r="B38" s="26" t="inlineStr">
+      <c r="B38" s="35" t="inlineStr">
         <is>
           <t>Metis Explorer</t>
         </is>
       </c>
-      <c r="C38" s="26" t="inlineStr">
+      <c r="C38" s="35" t="inlineStr">
         <is>
           <t>Andromeda Explorer</t>
         </is>
       </c>
-      <c r="D38" s="27" t="inlineStr">
+      <c r="D38" s="36" t="inlineStr">
         <is>
           <t>Metis is an Ethereum Layer-2 optimistic rollup featuring decentralized sequencers and hybrid rollup technology for improved censorship resistance and performance.</t>
         </is>
       </c>
-      <c r="E38" s="27" t="inlineStr">
+      <c r="E38" s="37" t="inlineStr">
         <is>
           <t>https://x.com/MetisDAO</t>
         </is>
       </c>
-      <c r="F38" s="27" t="inlineStr">
+      <c r="F38" s="37" t="inlineStr">
         <is>
           <t>https://metis.io</t>
         </is>
       </c>
-      <c r="G38" s="26" t="inlineStr">
+      <c r="G38" s="38" t="inlineStr">
         <is>
           <t>Metis</t>
         </is>
       </c>
-      <c r="H38" s="28" t="n"/>
-      <c r="I38" s="29" t="n"/>
-      <c r="J38" s="29" t="n"/>
-      <c r="K38" s="24" t="n"/>
-      <c r="L38" s="24" t="n"/>
-      <c r="M38" s="24" t="n"/>
-      <c r="N38" s="24" t="n"/>
-      <c r="O38" s="24" t="n"/>
-      <c r="P38" s="24" t="n"/>
-      <c r="Q38" s="24" t="n"/>
-      <c r="R38" s="24" t="n"/>
-      <c r="S38" s="24" t="n"/>
-      <c r="T38" s="24" t="n"/>
-      <c r="U38" s="24" t="n"/>
-      <c r="V38" s="24" t="n"/>
-      <c r="W38" s="24" t="n"/>
+      <c r="H38" s="39" t="n"/>
+      <c r="I38" s="39" t="n"/>
+      <c r="J38" s="39" t="n"/>
+      <c r="K38" s="16" t="n"/>
+      <c r="L38" s="6" t="n"/>
+      <c r="M38" s="6" t="n"/>
+      <c r="N38" s="6" t="n"/>
+      <c r="O38" s="6" t="n"/>
+      <c r="P38" s="6" t="n"/>
+      <c r="Q38" s="6" t="n"/>
+      <c r="R38" s="6" t="n"/>
+      <c r="S38" s="6" t="n"/>
+      <c r="T38" s="6" t="n"/>
+      <c r="U38" s="6" t="n"/>
+      <c r="V38" s="6" t="n"/>
+      <c r="W38" s="6" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="25" t="inlineStr">
+      <c r="A39" s="34" t="inlineStr">
         <is>
           <t>Boba Network</t>
         </is>
       </c>
-      <c r="B39" s="26" t="inlineStr">
+      <c r="B39" s="35" t="inlineStr">
         <is>
           <t>Bobascan</t>
         </is>
       </c>
-      <c r="C39" s="26" t="inlineStr">
+      <c r="C39" s="35" t="inlineStr">
         <is>
           <t>Boba Network Explorer</t>
         </is>
       </c>
-      <c r="D39" s="27" t="inlineStr">
+      <c r="D39" s="36" t="inlineStr">
         <is>
           <t>Boba Network is an Ethereum Layer-2 optimistic rollup featuring Hybrid Compute, allowing smart contracts to invoke off-chain data and computational resources.</t>
         </is>
       </c>
-      <c r="E39" s="27" t="inlineStr">
+      <c r="E39" s="37" t="inlineStr">
         <is>
           <t>https://x.com/bobanetwork</t>
         </is>
       </c>
-      <c r="F39" s="27" t="inlineStr">
+      <c r="F39" s="37" t="inlineStr">
         <is>
           <t>https://boba.network</t>
         </is>
       </c>
-      <c r="G39" s="27" t="inlineStr">
+      <c r="G39" s="40" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H39" s="28" t="n"/>
-      <c r="I39" s="29" t="n"/>
-      <c r="J39" s="25" t="n"/>
-      <c r="K39" s="24" t="n"/>
-      <c r="L39" s="24" t="n"/>
-      <c r="M39" s="24" t="n"/>
-      <c r="N39" s="24" t="n"/>
-      <c r="O39" s="24" t="n"/>
-      <c r="P39" s="24" t="n"/>
-      <c r="Q39" s="24" t="n"/>
-      <c r="R39" s="24" t="n"/>
-      <c r="S39" s="24" t="n"/>
-      <c r="T39" s="24" t="n"/>
-      <c r="U39" s="24" t="n"/>
-      <c r="V39" s="24" t="n"/>
-      <c r="W39" s="24" t="n"/>
+      <c r="H39" s="39" t="n"/>
+      <c r="I39" s="39" t="n"/>
+      <c r="J39" s="39" t="n"/>
+      <c r="K39" s="16" t="n"/>
+      <c r="L39" s="6" t="n"/>
+      <c r="M39" s="6" t="n"/>
+      <c r="N39" s="6" t="n"/>
+      <c r="O39" s="6" t="n"/>
+      <c r="P39" s="6" t="n"/>
+      <c r="Q39" s="6" t="n"/>
+      <c r="R39" s="6" t="n"/>
+      <c r="S39" s="6" t="n"/>
+      <c r="T39" s="6" t="n"/>
+      <c r="U39" s="6" t="n"/>
+      <c r="V39" s="6" t="n"/>
+      <c r="W39" s="6" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="25" t="inlineStr">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>zkSync Era</t>
         </is>
       </c>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B40" s="35" t="inlineStr">
         <is>
           <t>zkSync Explorer</t>
         </is>
       </c>
-      <c r="C40" s="26" t="inlineStr">
+      <c r="C40" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D40" s="27" t="inlineStr">
+      <c r="D40" s="36" t="inlineStr">
         <is>
           <t>zkSync Era is an EVM-compatible ZK rollup developed by Matter Labs, using zero-knowledge proofs for secure and scalable Ethereum transactions with native account abstraction.</t>
         </is>
       </c>
-      <c r="E40" s="27" t="inlineStr">
+      <c r="E40" s="37" t="inlineStr">
         <is>
           <t>https://x.com/zksync</t>
         </is>
       </c>
-      <c r="F40" s="27" t="inlineStr">
+      <c r="F40" s="37" t="inlineStr">
         <is>
           <t>https://zksync.io</t>
         </is>
       </c>
-      <c r="G40" s="26" t="inlineStr">
+      <c r="G40" s="38" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H40" s="28" t="n"/>
-      <c r="I40" s="29" t="n"/>
-      <c r="J40" s="29" t="n"/>
-      <c r="K40" s="24" t="n"/>
-      <c r="L40" s="24" t="n"/>
-      <c r="M40" s="24" t="n"/>
-      <c r="N40" s="24" t="n"/>
-      <c r="O40" s="24" t="n"/>
-      <c r="P40" s="24" t="n"/>
-      <c r="Q40" s="24" t="n"/>
-      <c r="R40" s="24" t="n"/>
-      <c r="S40" s="24" t="n"/>
-      <c r="T40" s="24" t="n"/>
-      <c r="U40" s="24" t="n"/>
-      <c r="V40" s="24" t="n"/>
-      <c r="W40" s="24" t="n"/>
+      <c r="H40" s="39" t="n"/>
+      <c r="I40" s="39" t="n"/>
+      <c r="J40" s="39" t="n"/>
+      <c r="K40" s="16" t="n"/>
+      <c r="L40" s="6" t="n"/>
+      <c r="M40" s="6" t="n"/>
+      <c r="N40" s="6" t="n"/>
+      <c r="O40" s="6" t="n"/>
+      <c r="P40" s="6" t="n"/>
+      <c r="Q40" s="6" t="n"/>
+      <c r="R40" s="6" t="n"/>
+      <c r="S40" s="6" t="n"/>
+      <c r="T40" s="6" t="n"/>
+      <c r="U40" s="6" t="n"/>
+      <c r="V40" s="6" t="n"/>
+      <c r="W40" s="6" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="25" t="inlineStr">
+      <c r="A41" s="34" t="inlineStr">
         <is>
           <t>Linea</t>
         </is>
       </c>
-      <c r="B41" s="26" t="inlineStr">
+      <c r="B41" s="35" t="inlineStr">
         <is>
           <t>Lineascan</t>
         </is>
       </c>
-      <c r="C41" s="26" t="inlineStr">
+      <c r="C41" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D41" s="27" t="inlineStr">
+      <c r="D41" s="36" t="inlineStr">
         <is>
           <t>Linea is an EVM-equivalent ZK rollup developed by ConsenSys, designed for seamless compatibility with Ethereum tooling while offering significantly reduced transaction costs.</t>
         </is>
       </c>
-      <c r="E41" s="27" t="inlineStr">
+      <c r="E41" s="37" t="inlineStr">
         <is>
           <t>https://x.com/LineaBuild</t>
         </is>
       </c>
-      <c r="F41" s="27" t="inlineStr">
+      <c r="F41" s="37" t="inlineStr">
         <is>
           <t>https://linea.build</t>
         </is>
       </c>
-      <c r="G41" s="26" t="inlineStr">
+      <c r="G41" s="38" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H41" s="28" t="n"/>
-      <c r="I41" s="29" t="n"/>
-      <c r="J41" s="29" t="n"/>
-      <c r="K41" s="24" t="n"/>
-      <c r="L41" s="24" t="n"/>
-      <c r="M41" s="24" t="n"/>
-      <c r="N41" s="24" t="n"/>
-      <c r="O41" s="24" t="n"/>
-      <c r="P41" s="24" t="n"/>
-      <c r="Q41" s="24" t="n"/>
-      <c r="R41" s="24" t="n"/>
-      <c r="S41" s="24" t="n"/>
-      <c r="T41" s="24" t="n"/>
-      <c r="U41" s="24" t="n"/>
-      <c r="V41" s="24" t="n"/>
-      <c r="W41" s="24" t="n"/>
+      <c r="H41" s="39" t="n"/>
+      <c r="I41" s="39" t="n"/>
+      <c r="J41" s="39" t="n"/>
+      <c r="K41" s="16" t="n"/>
+      <c r="L41" s="6" t="n"/>
+      <c r="M41" s="6" t="n"/>
+      <c r="N41" s="6" t="n"/>
+      <c r="O41" s="6" t="n"/>
+      <c r="P41" s="6" t="n"/>
+      <c r="Q41" s="6" t="n"/>
+      <c r="R41" s="6" t="n"/>
+      <c r="S41" s="6" t="n"/>
+      <c r="T41" s="6" t="n"/>
+      <c r="U41" s="6" t="n"/>
+      <c r="V41" s="6" t="n"/>
+      <c r="W41" s="6" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="25" t="inlineStr">
+      <c r="A42" s="34" t="inlineStr">
         <is>
           <t>Scroll</t>
         </is>
       </c>
-      <c r="B42" s="26" t="inlineStr">
+      <c r="B42" s="35" t="inlineStr">
         <is>
           <t>Scrollscan</t>
         </is>
       </c>
-      <c r="C42" s="26" t="inlineStr">
+      <c r="C42" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D42" s="27" t="inlineStr">
+      <c r="D42" s="36" t="inlineStr">
         <is>
           <t>Scroll is a native zkEVM Layer-2 on Ethereum providing bytecode-level EVM equivalence using zero-knowledge proof verification for trustless and scalable transactions.</t>
         </is>
       </c>
-      <c r="E42" s="27" t="inlineStr">
+      <c r="E42" s="37" t="inlineStr">
         <is>
           <t>https://x.com/Scroll_ZKP</t>
         </is>
       </c>
-      <c r="F42" s="27" t="inlineStr">
+      <c r="F42" s="37" t="inlineStr">
         <is>
           <t>https://scroll.io</t>
         </is>
       </c>
-      <c r="G42" s="26" t="inlineStr">
+      <c r="G42" s="38" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H42" s="28" t="n"/>
-      <c r="I42" s="29" t="n"/>
-      <c r="J42" s="29" t="n"/>
-      <c r="K42" s="24" t="n"/>
-      <c r="L42" s="24" t="n"/>
-      <c r="M42" s="24" t="n"/>
-      <c r="N42" s="24" t="n"/>
-      <c r="O42" s="24" t="n"/>
-      <c r="P42" s="24" t="n"/>
-      <c r="Q42" s="24" t="n"/>
-      <c r="R42" s="24" t="n"/>
-      <c r="S42" s="24" t="n"/>
-      <c r="T42" s="24" t="n"/>
-      <c r="U42" s="24" t="n"/>
-      <c r="V42" s="24" t="n"/>
-      <c r="W42" s="24" t="n"/>
+      <c r="H42" s="39" t="n"/>
+      <c r="I42" s="39" t="n"/>
+      <c r="J42" s="39" t="n"/>
+      <c r="K42" s="16" t="n"/>
+      <c r="L42" s="6" t="n"/>
+      <c r="M42" s="6" t="n"/>
+      <c r="N42" s="6" t="n"/>
+      <c r="O42" s="6" t="n"/>
+      <c r="P42" s="6" t="n"/>
+      <c r="Q42" s="6" t="n"/>
+      <c r="R42" s="6" t="n"/>
+      <c r="S42" s="6" t="n"/>
+      <c r="T42" s="6" t="n"/>
+      <c r="U42" s="6" t="n"/>
+      <c r="V42" s="6" t="n"/>
+      <c r="W42" s="6" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>Cronos</t>
-        </is>
-      </c>
-      <c r="B43" s="26" t="inlineStr">
-        <is>
-          <t>Cronoscan</t>
-        </is>
-      </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>OKLink</t>
-        </is>
-      </c>
-      <c r="D43" s="27" t="inlineStr">
-        <is>
-          <t>Cronos is an EVM-compatible Layer-1 blockchain developed by Crypto.com, enabling rapid porting of Ethereum and Cosmos DeFi apps with low fees and fast finality.</t>
-        </is>
-      </c>
-      <c r="E43" s="27" t="inlineStr">
-        <is>
-          <t>https://x.com/cronos_chain</t>
-        </is>
-      </c>
-      <c r="F43" s="27" t="inlineStr">
-        <is>
-          <t>https://cronos.org</t>
-        </is>
-      </c>
-      <c r="G43" s="26" t="inlineStr">
-        <is>
-          <t>Cronos</t>
-        </is>
-      </c>
-      <c r="H43" s="28" t="n"/>
-      <c r="I43" s="29" t="n"/>
-      <c r="J43" s="29" t="n"/>
-      <c r="K43" s="24" t="n"/>
-      <c r="L43" s="24" t="n"/>
-      <c r="M43" s="24" t="n"/>
-      <c r="N43" s="24" t="n"/>
-      <c r="O43" s="24" t="n"/>
-      <c r="P43" s="24" t="n"/>
-      <c r="Q43" s="24" t="n"/>
-      <c r="R43" s="24" t="n"/>
-      <c r="S43" s="24" t="n"/>
-      <c r="T43" s="24" t="n"/>
-      <c r="U43" s="24" t="n"/>
-      <c r="V43" s="24" t="n"/>
-      <c r="W43" s="24" t="n"/>
+      <c r="A43" s="34" t="inlineStr">
+        <is>
+          <t>Moonbeam</t>
+        </is>
+      </c>
+      <c r="B43" s="35" t="inlineStr">
+        <is>
+          <t>Moonscan</t>
+        </is>
+      </c>
+      <c r="C43" s="35" t="inlineStr">
+        <is>
+          <t>Blockscout</t>
+        </is>
+      </c>
+      <c r="D43" s="36" t="inlineStr">
+        <is>
+          <t>Moonbeam is a fully Ethereum-compatible smart contract parachain on Polkadot, enabling deployment of Ethereum dApps with minimal code modifications.</t>
+        </is>
+      </c>
+      <c r="E43" s="37" t="inlineStr">
+        <is>
+          <t>https://x.com/MoonbeamNetwork</t>
+        </is>
+      </c>
+      <c r="F43" s="37" t="inlineStr">
+        <is>
+          <t>https://moonbeam.network</t>
+        </is>
+      </c>
+      <c r="G43" s="38" t="inlineStr">
+        <is>
+          <t>Glimmer</t>
+        </is>
+      </c>
+      <c r="H43" s="39" t="n"/>
+      <c r="I43" s="39" t="n"/>
+      <c r="J43" s="39" t="n"/>
+      <c r="K43" s="16" t="n"/>
+      <c r="L43" s="6" t="n"/>
+      <c r="M43" s="6" t="n"/>
+      <c r="N43" s="6" t="n"/>
+      <c r="O43" s="6" t="n"/>
+      <c r="P43" s="6" t="n"/>
+      <c r="Q43" s="6" t="n"/>
+      <c r="R43" s="6" t="n"/>
+      <c r="S43" s="6" t="n"/>
+      <c r="T43" s="6" t="n"/>
+      <c r="U43" s="6" t="n"/>
+      <c r="V43" s="6" t="n"/>
+      <c r="W43" s="6" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>Moonbeam</t>
-        </is>
-      </c>
-      <c r="B44" s="26" t="inlineStr">
-        <is>
-          <t>Moonscan</t>
-        </is>
-      </c>
-      <c r="C44" s="26" t="inlineStr">
+      <c r="A44" s="34" t="inlineStr">
+        <is>
+          <t>Moonriver</t>
+        </is>
+      </c>
+      <c r="B44" s="35" t="inlineStr">
+        <is>
+          <t>Moonriver Moonscan</t>
+        </is>
+      </c>
+      <c r="C44" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D44" s="27" t="inlineStr">
-        <is>
-          <t>Moonbeam is a fully Ethereum-compatible smart contract parachain on Polkadot, enabling deployment of Ethereum dApps with minimal code modifications.</t>
-        </is>
-      </c>
-      <c r="E44" s="27" t="inlineStr">
-        <is>
-          <t>https://x.com/MoonbeamNetwork</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="inlineStr">
-        <is>
-          <t>https://moonbeam.network</t>
-        </is>
-      </c>
-      <c r="G44" s="26" t="inlineStr">
-        <is>
-          <t>Glimmer</t>
-        </is>
-      </c>
-      <c r="H44" s="28" t="n"/>
-      <c r="I44" s="29" t="n"/>
-      <c r="J44" s="29" t="n"/>
-      <c r="K44" s="24" t="n"/>
-      <c r="L44" s="24" t="n"/>
-      <c r="M44" s="24" t="n"/>
-      <c r="N44" s="24" t="n"/>
-      <c r="O44" s="24" t="n"/>
-      <c r="P44" s="24" t="n"/>
-      <c r="Q44" s="24" t="n"/>
-      <c r="R44" s="24" t="n"/>
-      <c r="S44" s="24" t="n"/>
-      <c r="T44" s="24" t="n"/>
-      <c r="U44" s="24" t="n"/>
-      <c r="V44" s="24" t="n"/>
-      <c r="W44" s="24" t="n"/>
+      <c r="D44" s="36" t="inlineStr">
+        <is>
+          <t>Moonriver is the canary network of Moonbeam deployed on Kusama, providing an Ethereum-compatible environment for testing and deploying new code in a live incentivized network.</t>
+        </is>
+      </c>
+      <c r="E44" s="37" t="inlineStr">
+        <is>
+          <t>https://x.com/MoonriverNW</t>
+        </is>
+      </c>
+      <c r="F44" s="37" t="inlineStr">
+        <is>
+          <t>https://moonbeam.network/networks/moonriver</t>
+        </is>
+      </c>
+      <c r="G44" s="38" t="inlineStr">
+        <is>
+          <t>Moonriver</t>
+        </is>
+      </c>
+      <c r="H44" s="39" t="n"/>
+      <c r="I44" s="39" t="n"/>
+      <c r="J44" s="39" t="n"/>
+      <c r="K44" s="16" t="n"/>
+      <c r="L44" s="6" t="n"/>
+      <c r="M44" s="6" t="n"/>
+      <c r="N44" s="6" t="n"/>
+      <c r="O44" s="6" t="n"/>
+      <c r="P44" s="6" t="n"/>
+      <c r="Q44" s="6" t="n"/>
+      <c r="R44" s="6" t="n"/>
+      <c r="S44" s="6" t="n"/>
+      <c r="T44" s="6" t="n"/>
+      <c r="U44" s="6" t="n"/>
+      <c r="V44" s="6" t="n"/>
+      <c r="W44" s="6" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>Moonriver</t>
-        </is>
-      </c>
-      <c r="B45" s="26" t="inlineStr">
-        <is>
-          <t>Moonriver Moonscan</t>
-        </is>
-      </c>
-      <c r="C45" s="26" t="inlineStr">
+      <c r="A45" s="34" t="inlineStr">
+        <is>
+          <t>Celo</t>
+        </is>
+      </c>
+      <c r="B45" s="35" t="inlineStr">
+        <is>
+          <t>Celoscan</t>
+        </is>
+      </c>
+      <c r="C45" s="35" t="inlineStr">
         <is>
           <t>Blockscout</t>
         </is>
       </c>
-      <c r="D45" s="27" t="inlineStr">
-        <is>
-          <t>Moonriver is the canary network of Moonbeam deployed on Kusama, providing an Ethereum-compatible environment for testing and deploying new code in a live incentivized network.</t>
-        </is>
-      </c>
-      <c r="E45" s="27" t="inlineStr">
-        <is>
-          <t>https://x.com/MoonriverNW</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="inlineStr">
-        <is>
-          <t>https://moonbeam.network/networks/moonriver</t>
-        </is>
-      </c>
-      <c r="G45" s="26" t="inlineStr">
-        <is>
-          <t>Moonriver</t>
-        </is>
-      </c>
-      <c r="H45" s="28" t="n"/>
-      <c r="I45" s="29" t="n"/>
-      <c r="J45" s="29" t="n"/>
-      <c r="K45" s="24" t="n"/>
-      <c r="L45" s="24" t="n"/>
-      <c r="M45" s="24" t="n"/>
-      <c r="N45" s="24" t="n"/>
-      <c r="O45" s="24" t="n"/>
-      <c r="P45" s="24" t="n"/>
-      <c r="Q45" s="24" t="n"/>
-      <c r="R45" s="24" t="n"/>
-      <c r="S45" s="24" t="n"/>
-      <c r="T45" s="24" t="n"/>
-      <c r="U45" s="24" t="n"/>
-      <c r="V45" s="24" t="n"/>
-      <c r="W45" s="24" t="n"/>
+      <c r="D45" s="36" t="inlineStr">
+        <is>
+          <t>Celo is an EVM-compatible Layer-1 blockchain focused on mobile-first financial inclusion, offering stable assets and fast, low-cost transactions for global DeFi access.</t>
+        </is>
+      </c>
+      <c r="E45" s="37" t="inlineStr">
+        <is>
+          <t>https://x.com/CeloOrg</t>
+        </is>
+      </c>
+      <c r="F45" s="37" t="inlineStr">
+        <is>
+          <t>https://celo.org</t>
+        </is>
+      </c>
+      <c r="G45" s="38" t="inlineStr">
+        <is>
+          <t>Celo</t>
+        </is>
+      </c>
+      <c r="H45" s="39" t="n"/>
+      <c r="I45" s="39" t="n"/>
+      <c r="J45" s="39" t="n"/>
+      <c r="K45" s="16" t="n"/>
+      <c r="L45" s="6" t="n"/>
+      <c r="M45" s="6" t="n"/>
+      <c r="N45" s="6" t="n"/>
+      <c r="O45" s="6" t="n"/>
+      <c r="P45" s="6" t="n"/>
+      <c r="Q45" s="6" t="n"/>
+      <c r="R45" s="6" t="n"/>
+      <c r="S45" s="6" t="n"/>
+      <c r="T45" s="6" t="n"/>
+      <c r="U45" s="6" t="n"/>
+      <c r="V45" s="6" t="n"/>
+      <c r="W45" s="6" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>Celo</t>
-        </is>
-      </c>
-      <c r="B46" s="26" t="inlineStr">
-        <is>
-          <t>Celoscan</t>
-        </is>
-      </c>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>Blockscout</t>
-        </is>
-      </c>
-      <c r="D46" s="27" t="inlineStr">
-        <is>
-          <t>Celo is an EVM-compatible Layer-1 blockchain focused on mobile-first financial inclusion, offering stable assets and fast, low-cost transactions for global DeFi access.</t>
-        </is>
-      </c>
-      <c r="E46" s="27" t="inlineStr">
-        <is>
-          <t>https://x.com/CeloOrg</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="inlineStr">
-        <is>
-          <t>https://celo.org</t>
-        </is>
-      </c>
-      <c r="G46" s="26" t="inlineStr">
-        <is>
-          <t>Celo</t>
-        </is>
-      </c>
-      <c r="H46" s="28" t="n"/>
-      <c r="I46" s="29" t="n"/>
-      <c r="J46" s="29" t="n"/>
-      <c r="K46" s="24" t="n"/>
-      <c r="L46" s="24" t="n"/>
-      <c r="M46" s="24" t="n"/>
-      <c r="N46" s="24" t="n"/>
-      <c r="O46" s="24" t="n"/>
-      <c r="P46" s="24" t="n"/>
-      <c r="Q46" s="24" t="n"/>
-      <c r="R46" s="24" t="n"/>
-      <c r="S46" s="24" t="n"/>
-      <c r="T46" s="24" t="n"/>
-      <c r="U46" s="24" t="n"/>
-      <c r="V46" s="24" t="n"/>
-      <c r="W46" s="24" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="25" t="inlineStr">
+      <c r="A46" s="34" t="inlineStr">
         <is>
           <t>Aurora</t>
         </is>
       </c>
-      <c r="B47" s="26" t="inlineStr">
+      <c r="B46" s="35" t="inlineStr">
         <is>
           <t>Aurora Explorer</t>
         </is>
       </c>
-      <c r="C47" s="26" t="inlineStr">
+      <c r="C46" s="35" t="inlineStr">
         <is>
           <t>AuroraScan</t>
         </is>
       </c>
-      <c r="D47" s="27" t="inlineStr">
+      <c r="D46" s="36" t="inlineStr">
         <is>
           <t>Aurora is an Ethereum Virtual Machine running on the NEAR Protocol, providing Ethereum developers a familiar environment with NEAR's scalability and near-zero transaction fees.</t>
         </is>
       </c>
-      <c r="E47" s="27" t="inlineStr">
+      <c r="E46" s="37" t="inlineStr">
         <is>
           <t>https://x.com/auroraisnear</t>
         </is>
       </c>
-      <c r="F47" s="27" t="inlineStr">
+      <c r="F46" s="37" t="inlineStr">
         <is>
           <t>https://aurora.dev</t>
         </is>
       </c>
-      <c r="G47" s="27" t="inlineStr">
+      <c r="G46" s="40" t="inlineStr">
         <is>
           <t>Ether</t>
         </is>
       </c>
-      <c r="H47" s="28" t="n"/>
-      <c r="I47" s="29" t="n"/>
-      <c r="J47" s="29" t="n"/>
-      <c r="K47" s="24" t="n"/>
-      <c r="L47" s="24" t="n"/>
-      <c r="M47" s="24" t="n"/>
-      <c r="N47" s="24" t="n"/>
-      <c r="O47" s="24" t="n"/>
-      <c r="P47" s="24" t="n"/>
-      <c r="Q47" s="24" t="n"/>
-      <c r="R47" s="24" t="n"/>
-      <c r="S47" s="24" t="n"/>
-      <c r="T47" s="24" t="n"/>
-      <c r="U47" s="24" t="n"/>
-      <c r="V47" s="24" t="n"/>
-      <c r="W47" s="24" t="n"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="25" t="n"/>
-      <c r="C48" s="25" t="n"/>
-      <c r="D48" s="29" t="n"/>
-      <c r="E48" s="29" t="n"/>
-      <c r="F48" s="25" t="n"/>
-      <c r="G48" s="29" t="n"/>
-      <c r="H48" s="28" t="n"/>
-      <c r="I48" s="29" t="n"/>
-      <c r="J48" s="29" t="n"/>
-      <c r="K48" s="24" t="n"/>
-      <c r="L48" s="24" t="n"/>
-      <c r="M48" s="24" t="n"/>
-      <c r="N48" s="24" t="n"/>
-      <c r="O48" s="24" t="n"/>
-      <c r="P48" s="24" t="n"/>
-      <c r="Q48" s="24" t="n"/>
-      <c r="R48" s="24" t="n"/>
-      <c r="S48" s="24" t="n"/>
-      <c r="T48" s="24" t="n"/>
-      <c r="U48" s="24" t="n"/>
-      <c r="V48" s="24" t="n"/>
-      <c r="W48" s="24" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="25" t="n"/>
-      <c r="C49" s="25" t="n"/>
-      <c r="D49" s="29" t="n"/>
-      <c r="E49" s="29" t="n"/>
-      <c r="F49" s="25" t="n"/>
-      <c r="G49" s="25" t="n"/>
-      <c r="H49" s="28" t="n"/>
-      <c r="I49" s="29" t="n"/>
-      <c r="J49" s="29" t="n"/>
-      <c r="K49" s="24" t="n"/>
-      <c r="L49" s="24" t="n"/>
-      <c r="M49" s="24" t="n"/>
-      <c r="N49" s="24" t="n"/>
-      <c r="O49" s="24" t="n"/>
-      <c r="P49" s="24" t="n"/>
-      <c r="Q49" s="24" t="n"/>
-      <c r="R49" s="24" t="n"/>
-      <c r="S49" s="24" t="n"/>
-      <c r="T49" s="24" t="n"/>
-      <c r="U49" s="24" t="n"/>
-      <c r="V49" s="24" t="n"/>
-      <c r="W49" s="24" t="n"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="25" t="n"/>
-      <c r="C50" s="25" t="n"/>
-      <c r="D50" s="29" t="n"/>
-      <c r="E50" s="29" t="n"/>
-      <c r="F50" s="25" t="n"/>
-      <c r="G50" s="25" t="n"/>
-      <c r="H50" s="28" t="n"/>
-      <c r="I50" s="29" t="n"/>
-      <c r="J50" s="29" t="n"/>
-      <c r="K50" s="24" t="n"/>
-      <c r="L50" s="24" t="n"/>
-      <c r="M50" s="24" t="n"/>
-      <c r="N50" s="24" t="n"/>
-      <c r="O50" s="24" t="n"/>
-      <c r="P50" s="24" t="n"/>
-      <c r="Q50" s="24" t="n"/>
-      <c r="R50" s="24" t="n"/>
-      <c r="S50" s="24" t="n"/>
-      <c r="T50" s="24" t="n"/>
-      <c r="U50" s="24" t="n"/>
-      <c r="V50" s="24" t="n"/>
-      <c r="W50" s="24" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="25" t="n"/>
-      <c r="B51" s="25" t="n"/>
-      <c r="C51" s="25" t="n"/>
-      <c r="D51" s="29" t="n"/>
-      <c r="E51" s="29" t="n"/>
-      <c r="F51" s="25" t="n"/>
-      <c r="G51" s="25" t="n"/>
-      <c r="H51" s="28" t="n"/>
-      <c r="I51" s="29" t="n"/>
-      <c r="J51" s="29" t="n"/>
-      <c r="K51" s="24" t="n"/>
-      <c r="L51" s="24" t="n"/>
-      <c r="M51" s="24" t="n"/>
-      <c r="N51" s="24" t="n"/>
-      <c r="O51" s="24" t="n"/>
-      <c r="P51" s="24" t="n"/>
-      <c r="Q51" s="24" t="n"/>
-      <c r="R51" s="24" t="n"/>
-      <c r="S51" s="24" t="n"/>
-      <c r="T51" s="24" t="n"/>
-      <c r="U51" s="24" t="n"/>
-      <c r="V51" s="24" t="n"/>
-      <c r="W51" s="24" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="25" t="n"/>
-      <c r="B52" s="25" t="n"/>
-      <c r="C52" s="25" t="n"/>
-      <c r="D52" s="29" t="n"/>
-      <c r="E52" s="29" t="n"/>
-      <c r="F52" s="25" t="n"/>
-      <c r="G52" s="25" t="n"/>
-      <c r="H52" s="28" t="n"/>
-      <c r="I52" s="29" t="n"/>
-      <c r="J52" s="29" t="n"/>
-      <c r="K52" s="24" t="n"/>
-      <c r="L52" s="24" t="n"/>
-      <c r="M52" s="24" t="n"/>
-      <c r="N52" s="24" t="n"/>
-      <c r="O52" s="24" t="n"/>
-      <c r="P52" s="24" t="n"/>
-      <c r="Q52" s="24" t="n"/>
-      <c r="R52" s="24" t="n"/>
-      <c r="S52" s="24" t="n"/>
-      <c r="T52" s="24" t="n"/>
-      <c r="U52" s="24" t="n"/>
-      <c r="V52" s="24" t="n"/>
-      <c r="W52" s="24" t="n"/>
-    </row>
-    <row r="53">
-      <c r="B53" s="25" t="n"/>
-      <c r="C53" s="25" t="n"/>
-      <c r="D53" s="29" t="n"/>
-      <c r="E53" s="29" t="n"/>
-      <c r="F53" s="25" t="n"/>
-      <c r="G53" s="25" t="n"/>
-      <c r="H53" s="28" t="n"/>
-      <c r="I53" s="29" t="n"/>
-      <c r="J53" s="29" t="n"/>
-      <c r="K53" s="24" t="n"/>
-      <c r="L53" s="24" t="n"/>
-      <c r="M53" s="24" t="n"/>
-      <c r="N53" s="24" t="n"/>
-      <c r="O53" s="24" t="n"/>
-      <c r="P53" s="24" t="n"/>
-      <c r="Q53" s="24" t="n"/>
-      <c r="R53" s="24" t="n"/>
-      <c r="S53" s="24" t="n"/>
-      <c r="T53" s="24" t="n"/>
-      <c r="U53" s="24" t="n"/>
-      <c r="V53" s="24" t="n"/>
-      <c r="W53" s="24" t="n"/>
-    </row>
-    <row r="54">
-      <c r="B54" s="25" t="n"/>
-      <c r="C54" s="25" t="n"/>
-      <c r="D54" s="29" t="n"/>
-      <c r="E54" s="29" t="n"/>
-      <c r="F54" s="25" t="n"/>
-      <c r="G54" s="25" t="n"/>
-      <c r="H54" s="28" t="n"/>
-      <c r="I54" s="29" t="n"/>
-      <c r="J54" s="29" t="n"/>
-      <c r="K54" s="24" t="n"/>
-      <c r="L54" s="24" t="n"/>
-      <c r="M54" s="24" t="n"/>
-      <c r="N54" s="24" t="n"/>
-      <c r="O54" s="24" t="n"/>
-      <c r="P54" s="24" t="n"/>
-      <c r="Q54" s="24" t="n"/>
-      <c r="R54" s="24" t="n"/>
-      <c r="S54" s="24" t="n"/>
-      <c r="T54" s="24" t="n"/>
-      <c r="U54" s="24" t="n"/>
-      <c r="V54" s="24" t="n"/>
-      <c r="W54" s="24" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="25" t="n"/>
-      <c r="B55" s="25" t="n"/>
-      <c r="C55" s="25" t="n"/>
-      <c r="D55" s="29" t="n"/>
-      <c r="E55" s="29" t="n"/>
-      <c r="F55" s="25" t="n"/>
-      <c r="G55" s="25" t="n"/>
-      <c r="H55" s="28" t="n"/>
-      <c r="I55" s="29" t="n"/>
-      <c r="J55" s="29" t="n"/>
-      <c r="K55" s="24" t="n"/>
-      <c r="L55" s="24" t="n"/>
-      <c r="M55" s="24" t="n"/>
-      <c r="N55" s="24" t="n"/>
-      <c r="O55" s="24" t="n"/>
-      <c r="P55" s="24" t="n"/>
-      <c r="Q55" s="24" t="n"/>
-      <c r="R55" s="24" t="n"/>
-      <c r="S55" s="24" t="n"/>
-      <c r="T55" s="24" t="n"/>
-      <c r="U55" s="24" t="n"/>
-      <c r="V55" s="24" t="n"/>
-      <c r="W55" s="24" t="n"/>
-    </row>
-    <row r="56">
-      <c r="B56" s="25" t="n"/>
-      <c r="C56" s="25" t="n"/>
-      <c r="D56" s="29" t="n"/>
-      <c r="E56" s="29" t="n"/>
-      <c r="F56" s="25" t="n"/>
-      <c r="G56" s="25" t="n"/>
-      <c r="H56" s="28" t="n"/>
-      <c r="I56" s="29" t="n"/>
-      <c r="J56" s="29" t="n"/>
-      <c r="K56" s="24" t="n"/>
-      <c r="L56" s="24" t="n"/>
-      <c r="M56" s="24" t="n"/>
-      <c r="N56" s="24" t="n"/>
-      <c r="O56" s="24" t="n"/>
-      <c r="P56" s="24" t="n"/>
-      <c r="Q56" s="24" t="n"/>
-      <c r="R56" s="24" t="n"/>
-      <c r="S56" s="24" t="n"/>
-      <c r="T56" s="24" t="n"/>
-      <c r="U56" s="24" t="n"/>
-      <c r="V56" s="24" t="n"/>
-      <c r="W56" s="24" t="n"/>
-    </row>
-    <row r="57">
-      <c r="B57" s="25" t="n"/>
-      <c r="C57" s="25" t="n"/>
-      <c r="D57" s="29" t="n"/>
-      <c r="E57" s="29" t="n"/>
-      <c r="F57" s="25" t="n"/>
-      <c r="G57" s="29" t="n"/>
-      <c r="H57" s="28" t="n"/>
-      <c r="I57" s="29" t="n"/>
-      <c r="J57" s="25" t="n"/>
-      <c r="K57" s="24" t="n"/>
-      <c r="L57" s="24" t="n"/>
-      <c r="M57" s="24" t="n"/>
-      <c r="N57" s="24" t="n"/>
-      <c r="O57" s="24" t="n"/>
-      <c r="P57" s="24" t="n"/>
-      <c r="Q57" s="24" t="n"/>
-      <c r="R57" s="24" t="n"/>
-      <c r="S57" s="24" t="n"/>
-      <c r="T57" s="24" t="n"/>
-      <c r="U57" s="24" t="n"/>
-      <c r="V57" s="24" t="n"/>
-      <c r="W57" s="24" t="n"/>
+      <c r="H46" s="39" t="n"/>
+      <c r="I46" s="39" t="n"/>
+      <c r="J46" s="39" t="n"/>
+      <c r="K46" s="16" t="n"/>
+      <c r="L46" s="6" t="n"/>
+      <c r="M46" s="6" t="n"/>
+      <c r="N46" s="6" t="n"/>
+      <c r="O46" s="6" t="n"/>
+      <c r="P46" s="6" t="n"/>
+      <c r="Q46" s="6" t="n"/>
+      <c r="R46" s="6" t="n"/>
+      <c r="S46" s="6" t="n"/>
+      <c r="T46" s="6" t="n"/>
+      <c r="U46" s="6" t="n"/>
+      <c r="V46" s="6" t="n"/>
+      <c r="W46" s="6" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9262,83 +9428,79 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId89"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Link block explorer for major networks.xlsx
+++ b/Link block explorer for major networks.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Etherscan is the leading blockchain explorer, search, API and analytics platform for Ethereum, a decentralized smart contracts platform.</t>
+          <t>The leading blockchain explorer, search, API and analytics platform for Ethereum, a decentralized smart contracts platform.</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Blockscout is an open-source blockchain explorer for Ethereum-based networks. It provides a comprehensive, easy-to-use interface for searching the blockchain and viewing transactions, blocks, addresses, and token transfers.</t>
+          <t>An open-source blockchain explorer for Ethereum-based networks. It provides a comprehensive, easy-to-use interface for searching the blockchain and viewing transactions, blocks, addresses, and token transfers.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Mempool.space is an open-source Bitcoin block explorer and mempool visualizer. It provides real-time data on Bitcoin transactions, blocks, fees, and network statistics.</t>
+          <t>An open-source Bitcoin block explorer and mempool visualizer. It provides real-time data on Bitcoin transactions, blocks, fees, and network statistics.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Blockchain.com Explorer is one of the oldest and most visited Bitcoin block explorers, providing data on Bitcoin transactions, blocks, and wallet addresses.</t>
+          <t>One of the oldest and most visited Bitcoin block explorers, providing data on Bitcoin transactions, blocks, and wallet addresses.</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>BscScan is the leading blockchain explorer for BNB Smart Chain, providing detailed information on transactions, smart contracts, tokens, and wallet activity.</t>
+          <t>The leading blockchain explorer for BNB Smart Chain, providing detailed information on transactions, smart contracts, tokens, and wallet activity.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Solscan is a user-friendly and real-time Solana blockchain explorer providing insights into transactions, accounts, tokens, and programs on the Solana network.</t>
+          <t>A user-friendly and real-time Solana blockchain explorer providing insights into transactions, accounts, tokens, and programs on the Solana network.</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Solana Explorer is the official block explorer maintained by Solana Foundation for inspecting transactions, accounts, blocks, and programs on the Solana network.</t>
+          <t>The official block explorer maintained by Solana Foundation for inspecting transactions, accounts, blocks, and programs on the Solana network.</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Avascan is the premier blockchain explorer for Avalanche, covering the C-Chain, X-Chain, P-Chain, and all Avalanche subnets.</t>
+          <t>The premier blockchain explorer for Avalanche, covering the C-Chain, X-Chain, P-Chain, and all Avalanche subnets.</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>SnowScan is a block explorer and analytics platform for the Avalanche C-Chain, operated by Etherscan.</t>
+          <t>A block explorer and analytics platform for the Avalanche C-Chain, operated by Etherscan.</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Polygonscan is the leading blockchain explorer for the Polygon PoS network, offering transaction lookups, smart contract verification, and token analytics.</t>
+          <t>The leading blockchain explorer for the Polygon PoS network, offering transaction lookups, smart contract verification, and token analytics.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>CardanoScan is a blockchain explorer and analytics platform for the Cardano network, supporting ADA transactions, staking, NFTs, and native tokens.</t>
+          <t>A blockchain explorer and analytics platform for the Cardano network, supporting ADA transactions, staking, NFTs, and native tokens.</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Adastat is an alternative Cardano blockchain explorer providing statistics on blocks, transactions, pools, and native assets.</t>
+          <t>An alternative Cardano blockchain explorer providing statistics on blocks, transactions, pools, and native assets.</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Tronscan is the official block explorer for the TRON blockchain, providing data on transactions, blocks, accounts, smart contracts, and DeFi activity.</t>
+          <t>The official block explorer for the TRON blockchain, providing data on transactions, blocks, accounts, smart contracts, and DeFi activity.</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>SonicScan is the leading blockchain explorer for the Sonic network, an EVM-compatible Layer-1 blockchain formerly known as Fantom. Powered by Etherscan, it provides comprehensive data on transactions, blocks, addresses, tokens, and smart contracts on the Sonic chain.</t>
+          <t>The leading blockchain explorer for the Sonic network, an EVM-compatible Layer-1 blockchain formerly known as Fantom. Powered by Etherscan, it provides comprehensive data on transactions, blocks, addresses, tokens, and smart contracts on the Sonic chain.</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>NearBlocks is a blockchain explorer and analytics platform for the NEAR Protocol, offering insights into transactions, accounts, tokens, and smart contracts.</t>
+          <t>A blockchain explorer and analytics platform for the NEAR Protocol, offering insights into transactions, accounts, tokens, and smart contracts.</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Allo.info is a blockchain explorer for the Algorand network, providing data on transactions, accounts, assets, and applications.</t>
+          <t>A blockchain explorer for the Algorand network, providing data on transactions, accounts, assets, and applications.</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Mintscan is a multi-chain blockchain explorer for the Cosmos ecosystem, covering the Cosmos Hub and all IBC-connected chains.</t>
+          <t>A multi-chain blockchain explorer for the Cosmos ecosystem, covering the Cosmos Hub and all IBC-connected chains.</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Subscan is a high-precision blockchain explorer for Substrate-based networks, covering Polkadot, Kusama, and all parachains.</t>
+          <t>A high-precision blockchain explorer for Substrate-based networks, covering Polkadot, Kusama, and all parachains.</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>XRPScan is a blockchain explorer and analytics platform for the XRP Ledger, providing data on transactions, accounts, tokens, and DEX activity.</t>
+          <t>A blockchain explorer and analytics platform for the XRP Ledger, providing data on transactions, accounts, tokens, and DEX activity.</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Bithomp is a blockchain explorer for the XRP Ledger focused on account lookups, username resolution, NFTs, and payment history.</t>
+          <t>A blockchain explorer for the XRP Ledger focused on account lookups, username resolution, NFTs, and payment history.</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>TzKT is an open-source, high-performance blockchain explorer and API for the Tezos network, supporting transactions, smart contracts, tokens, and baking data.</t>
+          <t>An open-source, high-performance blockchain explorer and API for the Tezos network, supporting transactions, smart contracts, tokens, and baking data.</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>HashScan is the official explorer for the Hedera network, providing data on transactions, tokens, smart contracts, and network consensus.</t>
+          <t>The official explorer for the Hedera network, providing data on transactions, tokens, smart contracts, and network consensus.</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Aptos Explorer is the official block explorer maintained by Aptos Labs for browsing transactions, accounts, tokens, and modules on the Aptos blockchain.</t>
+          <t>The official block explorer maintained by Aptos Labs for browsing transactions, accounts, tokens, and modules on the Aptos blockchain.</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>SuiVision is the most widely used block explorer for the Sui blockchain, providing detailed views of transactions, objects, accounts, and packages.</t>
+          <t>The most widely used block explorer for the Sui blockchain, providing detailed views of transactions, objects, accounts, and packages.</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Seitrace is the official block explorer for the Sei network, offering transaction lookup, contract verification, and token analytics.</t>
+          <t>The official block explorer for the Sei network, offering transaction lookup, contract verification, and token analytics.</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Kaiascan is the official block explorer for the Kaia (formerly Klaytn) blockchain, covering transactions, blocks, accounts, and smart contracts.</t>
+          <t>The official block explorer for the Kaia (formerly Klaytn) blockchain, covering transactions, blocks, accounts, and smart contracts.</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Harmony Explorer is the official block explorer for the Harmony blockchain, providing data on transactions, blocks, staking, and smart contracts.</t>
+          <t>The official block explorer for the Harmony blockchain, providing data on transactions, blocks, staking, and smart contracts.</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Arbiscan is the leading blockchain explorer for Arbitrum One, providing transaction history, smart contract data, token transfers, and gas analytics.</t>
+          <t>The leading blockchain explorer for Arbitrum One, providing transaction history, smart contract data, token transfers, and gas analytics.</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Optimistic Etherscan is the primary block explorer for the Optimism network, offering full transaction, contract, and token visibility.</t>
+          <t>The primary block explorer for the Optimism network, offering full transaction, contract, and token visibility.</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>BaseScan is the leading blockchain explorer for Base, Coinbase's Ethereum L2 network, providing transaction lookup, smart contract verification, and token analytics.</t>
+          <t>The leading blockchain explorer for Base, Coinbase's Ethereum L2 network, providing transaction lookup, smart contract verification, and token analytics.</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Blastscan is the official block explorer for the Blast network, an Ethereum L2 with native yield for ETH and stablecoins.</t>
+          <t>The official block explorer for the Blast network, an Ethereum L2 with native yield for ETH and stablecoins.</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Metis Explorer is the official block explorer for the Metis Andromeda L2 network, providing transaction and smart contract data.</t>
+          <t>The official block explorer for the Metis Andromeda L2 network, providing transaction and smart contract data.</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Bobascan is the official block explorer for Boba Network, an Ethereum L2 focused on fast exits and hybrid compute.</t>
+          <t>The official block explorer for Boba Network, an Ethereum L2 focused on fast exits and hybrid compute.</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>zkSync Explorer is the official block explorer for zkSync Era, a ZK rollup developed by Matter Labs, supporting transactions, tokens, and smart contracts.</t>
+          <t>The official block explorer for zkSync Era, a ZK rollup developed by Matter Labs, supporting transactions, tokens, and smart contracts.</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Starkscan is a leading block explorer for Starknet, a ZK rollup on Ethereum, supporting transactions, contracts, tokens, and Cairo classes.</t>
+          <t>A leading block explorer for Starknet, a ZK rollup on Ethereum, supporting transactions, contracts, tokens, and Cairo classes.</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Voyager is an alternative Starknet block explorer developed by Nethermind, providing transaction lookup, contract verification, and network analytics.</t>
+          <t>An alternative Starknet block explorer developed by Nethermind, providing transaction lookup, contract verification, and network analytics.</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Lineascan is the official block explorer for Linea, a ZK rollup developed by ConsenSys, offering transaction and smart contract data.</t>
+          <t>The official block explorer for Linea, a ZK rollup developed by ConsenSys, offering transaction and smart contract data.</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Scrollscan is the official block explorer for Scroll, a ZK rollup on Ethereum, providing full transaction, contract, and token analytics.</t>
+          <t>The official block explorer for Scroll, a ZK rollup on Ethereum, providing full transaction, contract, and token analytics.</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Gnosisscan is the primary block explorer for Gnosis Chain (formerly xDai), providing transaction history, smart contract data, and token analytics.</t>
+          <t>The primary block explorer for Gnosis Chain (formerly xDai), providing transaction history, smart contract data, and token analytics.</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Cronoscan is the leading block explorer for the Cronos blockchain, the EVM-compatible chain developed by Crypto.com.</t>
+          <t>The leading block explorer for the Cronos blockchain, the EVM-compatible chain developed by Crypto.com.</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Moonscan is the primary block explorer for Moonbeam, a Polkadot parachain providing full Ethereum compatibility.</t>
+          <t>The primary block explorer for Moonbeam, a Polkadot parachain providing full Ethereum compatibility.</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Moonriver Moonscan is the block explorer for Moonriver, the Kusama-based canary network of Moonbeam.</t>
+          <t>The block explorer for Moonriver, the Kusama-based canary network of Moonbeam.</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Celoscan is the leading block explorer for the Celo network, an EVM-compatible blockchain focused on mobile-first DeFi.</t>
+          <t>The leading block explorer for the Celo network, an EVM-compatible blockchain focused on mobile-first DeFi.</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Aurora Explorer is the official block explorer for Aurora, an EVM environment running on the NEAR Protocol.</t>
+          <t>The official block explorer for Aurora, an EVM environment running on the NEAR Protocol.</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2919,14 +2919,14 @@
       <c r="J48" s="6" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>Gnosis Beacon Chain Explorer</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Gnosis Beacon Chain Explorer is the official validator and staking explorer for the Gnosis Beacon Chain, built by Bitfly. It provides detailed data on validators, epochs, slots, and staking rewards on the Gnosis network.</t>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>The official validator and staking explorer for the Gnosis Beacon Chain, built by Bitfly. It provides detailed data on validators, epochs, slots, and staking rewards on the Gnosis network.</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -2934,12 +2934,12 @@
           <t>Gnosis Chain</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>https://beaconchain.gnosischain.com</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="0" t="inlineStr">
         <is>
           <t>https://github.com/gobitfly/eth2-beaconchain-explorer</t>
         </is>
@@ -2947,14 +2947,14 @@
       <c r="H49" s="8" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>3xpl</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>3xpl is a universal blockchain explorer supporting 48+ blockchains including Gnosis Chain, offering lightning-fast block and transaction lookup with no ads and maximum privacy.</t>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>A universal blockchain explorer supporting 48+ blockchains including Gnosis Chain, offering lightning-fast block and transaction lookup with no ads and maximum privacy.</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
@@ -2962,17 +2962,17 @@
           <t>Gnosis Chain</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>https://3xpl.com</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>https://x.com/3xplcom</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="0" t="inlineStr">
         <is>
           <t>https://github.com/3xplcom</t>
         </is>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>Ethereum is the leading decentralized smart contract platform enabling DeFi, NFTs, and dApps through its EVM. It transitioned to proof-of-stake via The Merge in 2022.</t>
+          <t>The leading decentralized smart contract platform enabling DeFi, NFTs, and dApps through its EVM. It transitioned to proof-of-stake via The Merge in 2022.</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>Bitcoin is the world's first decentralized peer-to-peer digital currency, created by Satoshi Nakamoto in 2009 and secured by proof-of-work mining.</t>
+          <t>The world's first decentralized peer-to-peer digital currency, created by Satoshi Nakamoto in 2009 and secured by proof-of-work mining.</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Solana is a high-performance Layer-1 blockchain using Proof of History and Proof of Stake, capable of processing thousands of transactions per second with low fees.</t>
+          <t>A high-performance Layer-1 blockchain using Proof of History and Proof of Stake, capable of processing thousands of transactions per second with low fees.</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Avalanche is a Layer-1 blockchain with a multi-chain architecture (C-Chain, X-Chain, P-Chain) offering high throughput and sub-second finality via the Avalanche consensus protocol.</t>
+          <t>A Layer-1 blockchain with a multi-chain architecture (C-Chain, X-Chain, P-Chain) offering high throughput and sub-second finality via the Avalanche consensus protocol.</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Cardano is a peer-reviewed proof-of-stake blockchain developed by IOHK, featuring the Ouroboros consensus protocol and native multi-asset and NFT support.</t>
+          <t>A peer-reviewed proof-of-stake blockchain developed by IOHK, featuring the Ouroboros consensus protocol and native multi-asset and NFT support.</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Starknet is a permissionless ZK rollup on Ethereum developed by StarkWare, using STARK cryptographic proofs for scalable computation with native account abstraction.</t>
+          <t>A permissionless ZK rollup on Ethereum developed by StarkWare, using STARK cryptographic proofs for scalable computation with native account abstraction.</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>Ethereum Classic is the original Ethereum blockchain that preserved immutability after the 2016 DAO hack, supporting smart contracts and secured by proof-of-work.</t>
+          <t>The original Ethereum blockchain that preserved immutability after the 2016 DAO hack, supporting smart contracts and secured by proof-of-work.</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="D11" s="36" t="inlineStr">
         <is>
-          <t>Base is an Ethereum Layer-2 network built by Coinbase using the OP Stack, offering low-cost EVM-compatible transactions with seamless access to Coinbase's ecosystem.</t>
+          <t>An Ethereum Layer-2 network built by Coinbase using the OP Stack, offering low-cost EVM-compatible transactions with seamless access to Coinbase's ecosystem.</t>
         </is>
       </c>
       <c r="E11" s="37" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="D12" s="36" t="inlineStr">
         <is>
-          <t>Optimism is an Ethereum Layer-2 optimistic rollup providing EVM-equivalent scalability with a fraud-proof security model, governed by the Optimism Collective.</t>
+          <t>An Ethereum Layer-2 optimistic rollup providing EVM-equivalent scalability with a fraud-proof security model, governed by the Optimism Collective.</t>
         </is>
       </c>
       <c r="E12" s="37" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="D13" s="36" t="inlineStr">
         <is>
-          <t>Arbitrum One is an Ethereum Layer-2 optimistic rollup developed by Offchain Labs, delivering high throughput and low fees with full EVM compatibility.</t>
+          <t>An Ethereum Layer-2 optimistic rollup developed by Offchain Labs, delivering high throughput and low fees with full EVM compatibility.</t>
         </is>
       </c>
       <c r="E13" s="37" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="D15" s="36" t="inlineStr">
         <is>
-          <t>zkSync Era is an EVM-compatible ZK rollup developed by Matter Labs, using zero-knowledge proofs for secure and scalable Ethereum transactions with native account abstraction.</t>
+          <t>An EVM-compatible ZK rollup developed by Matter Labs, using zero-knowledge proofs for secure and scalable Ethereum transactions with native account abstraction.</t>
         </is>
       </c>
       <c r="E15" s="37" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="D16" s="36" t="inlineStr">
         <is>
-          <t>Scroll is a native zkEVM Layer-2 on Ethereum providing bytecode-level EVM equivalence using zero-knowledge proof verification for trustless and scalable transactions.</t>
+          <t>A native zkEVM Layer-2 on Ethereum providing bytecode-level EVM equivalence using zero-knowledge proof verification for trustless and scalable transactions.</t>
         </is>
       </c>
       <c r="E16" s="37" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D17" s="36" t="inlineStr">
         <is>
-          <t>Linea is an EVM-equivalent ZK rollup developed by ConsenSys, designed for seamless compatibility with Ethereum tooling while offering significantly reduced transaction costs.</t>
+          <t>An EVM-equivalent ZK rollup developed by ConsenSys, designed for seamless compatibility with Ethereum tooling while offering significantly reduced transaction costs.</t>
         </is>
       </c>
       <c r="E17" s="37" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D18" s="36" t="inlineStr">
         <is>
-          <t>BNB Smart Chain is a high-performance EVM-compatible blockchain developed by Binance, supporting DeFi, NFTs, and Web3 applications with low transaction fees.</t>
+          <t>A high-performance EVM-compatible blockchain developed by Binance, supporting DeFi, NFTs, and Web3 applications with low transaction fees.</t>
         </is>
       </c>
       <c r="E18" s="37" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="D19" s="36" t="inlineStr">
         <is>
-          <t>TRON is a high-throughput Layer-1 blockchain focused on digital entertainment and content distribution, featuring a large DeFi ecosystem and the world's largest USDT circulation.</t>
+          <t>A high-throughput Layer-1 blockchain focused on digital entertainment and content distribution, featuring a large DeFi ecosystem and the world's largest USDT circulation.</t>
         </is>
       </c>
       <c r="E19" s="37" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="D20" s="36" t="inlineStr">
         <is>
-          <t>Sonic is an EVM-compatible Layer-1 blockchain evolved from Fantom Opera, offering sub-second finality and a developer fee monetization program via Sonic Labs.</t>
+          <t>An EVM-compatible Layer-1 blockchain evolved from Fantom Opera, offering sub-second finality and a developer fee monetization program via Sonic Labs.</t>
         </is>
       </c>
       <c r="E20" s="37" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="D21" s="36" t="inlineStr">
         <is>
-          <t>NEAR Protocol is a sharded, proof-of-stake Layer-1 blockchain designed for usability and scalability, featuring human-readable account names and low-cost smart contracts.</t>
+          <t>A sharded, proof-of-stake Layer-1 blockchain designed for usability and scalability, featuring human-readable account names and low-cost smart contracts.</t>
         </is>
       </c>
       <c r="E21" s="37" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="D22" s="36" t="inlineStr">
         <is>
-          <t>Algorand is a pure proof-of-stake Layer-1 blockchain offering instant transaction finality, carbon neutrality, and support for smart contracts and digital assets via AVM.</t>
+          <t>A pure proof-of-stake Layer-1 blockchain offering instant transaction finality, carbon neutrality, and support for smart contracts and digital assets via AVM.</t>
         </is>
       </c>
       <c r="E22" s="37" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="D23" s="36" t="inlineStr">
         <is>
-          <t>Cosmos Hub is the central blockchain of the Cosmos ecosystem, enabling inter-blockchain communication (IBC) between sovereign chains and serving as the network's main security hub.</t>
+          <t>The central blockchain of the Cosmos ecosystem, enabling inter-blockchain communication (IBC) between sovereign chains and serving as the network's main security hub.</t>
         </is>
       </c>
       <c r="E23" s="37" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="D24" s="36" t="inlineStr">
         <is>
-          <t>Polkadot is a multichain network developed by Parity Technologies enabling interoperability between specialized blockchains called parachains via a central Relay Chain.</t>
+          <t>A multichain network developed by Parity Technologies enabling interoperability between specialized blockchains called parachains via a central Relay Chain.</t>
         </is>
       </c>
       <c r="E24" s="37" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="D25" s="36" t="inlineStr">
         <is>
-          <t>Stellar is an open-source payment network designed for fast, affordable cross-border transactions and digital asset issuance, widely adopted by financial institutions globally.</t>
+          <t>An open-source payment network designed for fast, affordable cross-border transactions and digital asset issuance, widely adopted by financial institutions globally.</t>
         </is>
       </c>
       <c r="E25" s="37" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="D26" s="36" t="inlineStr">
         <is>
-          <t>Tezos is a self-amending Layer-1 blockchain using liquid proof-of-stake, featuring on-chain governance and formal verification of smart contracts written in Michelson.</t>
+          <t>A self-amending Layer-1 blockchain using liquid proof-of-stake, featuring on-chain governance and formal verification of smart contracts written in Michelson.</t>
         </is>
       </c>
       <c r="E26" s="37" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="D27" s="36" t="inlineStr">
         <is>
-          <t>Hedera is a public distributed ledger using hashgraph consensus, offering high-throughput, low-latency transactions governed by a council of leading global enterprises.</t>
+          <t>A public distributed ledger using hashgraph consensus, offering high-throughput, low-latency transactions governed by a council of leading global enterprises.</t>
         </is>
       </c>
       <c r="E27" s="37" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="D28" s="36" t="inlineStr">
         <is>
-          <t>Aptos is a Layer-1 blockchain developed by former Meta engineers using the Move programming language, featuring parallel transaction execution for high throughput and safety.</t>
+          <t>A Layer-1 blockchain developed by former Meta engineers using the Move programming language, featuring parallel transaction execution for high throughput and safety.</t>
         </is>
       </c>
       <c r="E28" s="37" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="D29" s="36" t="inlineStr">
         <is>
-          <t>Sui is a Layer-1 blockchain developed by Mysten Labs using the Move language, featuring an object-centric data model and parallel transaction processing for high performance.</t>
+          <t>A Layer-1 blockchain developed by Mysten Labs using the Move language, featuring an object-centric data model and parallel transaction processing for high performance.</t>
         </is>
       </c>
       <c r="E29" s="37" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="D30" s="36" t="inlineStr">
         <is>
-          <t>Sei is a Layer-1 blockchain optimized for trading applications, featuring parallelized EVM execution, twin-turbo consensus, and native order book primitives in the protocol.</t>
+          <t>A Layer-1 blockchain optimized for trading applications, featuring parallelized EVM execution, twin-turbo consensus, and native order book primitives in the protocol.</t>
         </is>
       </c>
       <c r="E30" s="37" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="D32" s="36" t="inlineStr">
         <is>
-          <t>Harmony is a sharded proof-of-stake Layer-1 blockchain focused on cross-chain bridging and decentralized applications, using effective proof-of-stake for fast finality.</t>
+          <t>A sharded proof-of-stake Layer-1 blockchain focused on cross-chain bridging and decentralized applications, using effective proof-of-stake for fast finality.</t>
         </is>
       </c>
       <c r="E32" s="37" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="D33" s="36" t="inlineStr">
         <is>
-          <t>Arbitrum One is an Ethereum Layer-2 optimistic rollup developed by Offchain Labs, delivering high throughput and low fees with full EVM compatibility.</t>
+          <t>An Ethereum Layer-2 optimistic rollup developed by Offchain Labs, delivering high throughput and low fees with full EVM compatibility.</t>
         </is>
       </c>
       <c r="E33" s="37" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
-          <t>Optimism is an Ethereum Layer-2 optimistic rollup providing EVM-equivalent scalability with a fraud-proof security model, governed by the Optimism Collective.</t>
+          <t>An Ethereum Layer-2 optimistic rollup providing EVM-equivalent scalability with a fraud-proof security model, governed by the Optimism Collective.</t>
         </is>
       </c>
       <c r="E34" s="37" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="D35" s="36" t="inlineStr">
         <is>
-          <t>Base is an Ethereum Layer-2 network built by Coinbase using the OP Stack, offering low-cost EVM-compatible transactions with seamless access to Coinbase's ecosystem.</t>
+          <t>An Ethereum Layer-2 network built by Coinbase using the OP Stack, offering low-cost EVM-compatible transactions with seamless access to Coinbase's ecosystem.</t>
         </is>
       </c>
       <c r="E35" s="37" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="D36" s="36" t="inlineStr">
         <is>
-          <t>Blast is an Ethereum Layer-2 optimistic rollup offering native yield for ETH and stablecoins through automatic rebasing, built by the team behind the Blur NFT marketplace.</t>
+          <t>An Ethereum Layer-2 optimistic rollup offering native yield for ETH and stablecoins through automatic rebasing, built by the team behind the Blur NFT marketplace.</t>
         </is>
       </c>
       <c r="E36" s="37" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="D37" s="36" t="inlineStr">
         <is>
-          <t>Mantle is an Ethereum Layer-2 network using optimistic rollup technology with modular data availability via EigenDA, using MNT as its native gas token.</t>
+          <t>An Ethereum Layer-2 network using optimistic rollup technology with modular data availability via EigenDA, using MNT as its native gas token.</t>
         </is>
       </c>
       <c r="E37" s="37" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="D38" s="36" t="inlineStr">
         <is>
-          <t>Metis is an Ethereum Layer-2 optimistic rollup featuring decentralized sequencers and hybrid rollup technology for improved censorship resistance and performance.</t>
+          <t>An Ethereum Layer-2 optimistic rollup featuring decentralized sequencers and hybrid rollup technology for improved censorship resistance and performance.</t>
         </is>
       </c>
       <c r="E38" s="37" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="D39" s="36" t="inlineStr">
         <is>
-          <t>Boba Network is an Ethereum Layer-2 optimistic rollup featuring Hybrid Compute, allowing smart contracts to invoke off-chain data and computational resources.</t>
+          <t>An Ethereum Layer-2 optimistic rollup featuring Hybrid Compute, allowing smart contracts to invoke off-chain data and computational resources.</t>
         </is>
       </c>
       <c r="E39" s="37" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="D40" s="36" t="inlineStr">
         <is>
-          <t>zkSync Era is an EVM-compatible ZK rollup developed by Matter Labs, using zero-knowledge proofs for secure and scalable Ethereum transactions with native account abstraction.</t>
+          <t>An EVM-compatible ZK rollup developed by Matter Labs, using zero-knowledge proofs for secure and scalable Ethereum transactions with native account abstraction.</t>
         </is>
       </c>
       <c r="E40" s="37" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="D41" s="36" t="inlineStr">
         <is>
-          <t>Linea is an EVM-equivalent ZK rollup developed by ConsenSys, designed for seamless compatibility with Ethereum tooling while offering significantly reduced transaction costs.</t>
+          <t>An EVM-equivalent ZK rollup developed by ConsenSys, designed for seamless compatibility with Ethereum tooling while offering significantly reduced transaction costs.</t>
         </is>
       </c>
       <c r="E41" s="37" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="D42" s="36" t="inlineStr">
         <is>
-          <t>Scroll is a native zkEVM Layer-2 on Ethereum providing bytecode-level EVM equivalence using zero-knowledge proof verification for trustless and scalable transactions.</t>
+          <t>A native zkEVM Layer-2 on Ethereum providing bytecode-level EVM equivalence using zero-knowledge proof verification for trustless and scalable transactions.</t>
         </is>
       </c>
       <c r="E42" s="37" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="D43" s="36" t="inlineStr">
         <is>
-          <t>Moonbeam is a fully Ethereum-compatible smart contract parachain on Polkadot, enabling deployment of Ethereum dApps with minimal code modifications.</t>
+          <t>A fully Ethereum-compatible smart contract parachain on Polkadot, enabling deployment of Ethereum dApps with minimal code modifications.</t>
         </is>
       </c>
       <c r="E43" s="37" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="D44" s="36" t="inlineStr">
         <is>
-          <t>Moonriver is the canary network of Moonbeam deployed on Kusama, providing an Ethereum-compatible environment for testing and deploying new code in a live incentivized network.</t>
+          <t>The canary network of Moonbeam deployed on Kusama, providing an Ethereum-compatible environment for testing and deploying new code in a live incentivized network.</t>
         </is>
       </c>
       <c r="E44" s="37" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="D45" s="36" t="inlineStr">
         <is>
-          <t>Celo is an EVM-compatible Layer-1 blockchain focused on mobile-first financial inclusion, offering stable assets and fast, low-cost transactions for global DeFi access.</t>
+          <t>An EVM-compatible Layer-1 blockchain focused on mobile-first financial inclusion, offering stable assets and fast, low-cost transactions for global DeFi access.</t>
         </is>
       </c>
       <c r="E45" s="37" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="D46" s="36" t="inlineStr">
         <is>
-          <t>Aurora is an Ethereum Virtual Machine running on the NEAR Protocol, providing Ethereum developers a familiar environment with NEAR's scalability and near-zero transaction fees.</t>
+          <t>An Ethereum Virtual Machine running on the NEAR Protocol, providing Ethereum developers a familiar environment with NEAR's scalability and near-zero transaction fees.</t>
         </is>
       </c>
       <c r="E46" s="37" t="inlineStr">
